--- a/tier.xlsx
+++ b/tier.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyung\Desktop\새 폴더 (3)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyung\Desktop\새 폴더 (1)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2456335E-D49D-48CD-A608-405135EF85C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE520E0C-F7FE-4A48-9F4F-6AD5E15BFD95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{B5D2F30C-64E4-4785-A390-F7C9B2DB27D6}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1492" uniqueCount="634">
   <si>
     <t>순번</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1304,10 +1304,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>떠아콩</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>케이대</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2245,14 +2241,38 @@
     <t>jooyoung0040</t>
   </si>
   <si>
-    <t>또아임니더</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1004yomi</t>
   </si>
   <si>
     <t>날짜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이미지값</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영상값</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이미지유무</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영상유무</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>넘버링</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>떠아</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>또아</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2620,16 +2640,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54A2A291-B3BF-4EBE-93A6-386812DCA76D}">
-  <dimension ref="A1:G297"/>
+  <dimension ref="A1:L297"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="2" max="2" width="10.9375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.125" customWidth="1"/>
     <col min="6" max="6" width="14.5625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21.75" customWidth="1"/>
+    <col min="8" max="8" width="23.625" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="10" max="10" width="13.5" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2649,10 +2673,25 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
+        <v>626</v>
+      </c>
+      <c r="H1" t="s">
+        <v>627</v>
+      </c>
+      <c r="I1" t="s">
         <v>628</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.6">
+      <c r="J1" t="s">
+        <v>629</v>
+      </c>
+      <c r="K1" t="s">
+        <v>630</v>
+      </c>
+      <c r="L1" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2669,13 +2708,25 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G2" s="1">
-        <v>46163</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.6">
+        <v>46167</v>
+      </c>
+      <c r="H2" t="str">
+        <f>IF(J2=1,L2&amp;".png","")</f>
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <f>IF(K2=1,L2&amp;".mp4","")</f>
+        <v/>
+      </c>
+      <c r="L2">
+        <f>1000+A2</f>
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2692,10 +2743,22 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.6">
+        <v>331</v>
+      </c>
+      <c r="H3" t="str">
+        <f t="shared" ref="H3:H66" si="0">IF(J3=1,L3&amp;".png","")</f>
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" ref="I3:I66" si="1">IF(K3=1,L3&amp;".mp4","")</f>
+        <v/>
+      </c>
+      <c r="L3">
+        <f t="shared" ref="L3:L66" si="2">1000+A3</f>
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2712,10 +2775,22 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.6">
+        <v>332</v>
+      </c>
+      <c r="H4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L4">
+        <f t="shared" si="2"/>
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2723,7 +2798,7 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -2732,10 +2807,22 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.6">
+        <v>333</v>
+      </c>
+      <c r="H5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L5">
+        <f t="shared" si="2"/>
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2752,10 +2839,22 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.6">
+        <v>334</v>
+      </c>
+      <c r="H6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L6">
+        <f t="shared" si="2"/>
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2772,10 +2871,22 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.6">
+        <v>335</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L7">
+        <f t="shared" si="2"/>
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2783,7 +2894,7 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -2792,10 +2903,22 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.6">
+        <v>336</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L8">
+        <f t="shared" si="2"/>
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2803,7 +2926,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -2812,10 +2935,22 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.6">
+        <v>337</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L9">
+        <f t="shared" si="2"/>
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2823,7 +2958,7 @@
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -2832,10 +2967,22 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.6">
+        <v>338</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L10">
+        <f t="shared" si="2"/>
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2843,7 +2990,7 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D11" t="s">
         <v>21</v>
@@ -2852,10 +2999,22 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.6">
+        <v>339</v>
+      </c>
+      <c r="H11" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L11">
+        <f t="shared" si="2"/>
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2872,10 +3031,22 @@
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.6">
+        <v>340</v>
+      </c>
+      <c r="H12" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L12">
+        <f t="shared" si="2"/>
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2892,10 +3063,22 @@
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.6">
+        <v>341</v>
+      </c>
+      <c r="H13" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L13">
+        <f t="shared" si="2"/>
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2903,7 +3086,7 @@
         <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D14" t="s">
         <v>26</v>
@@ -2912,10 +3095,22 @@
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.6">
+        <v>342</v>
+      </c>
+      <c r="H14" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L14">
+        <f t="shared" si="2"/>
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2932,10 +3127,22 @@
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.6">
+        <v>343</v>
+      </c>
+      <c r="H15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L15">
+        <f t="shared" si="2"/>
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2952,10 +3159,22 @@
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.6">
+        <v>344</v>
+      </c>
+      <c r="H16" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L16">
+        <f t="shared" si="2"/>
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2972,10 +3191,22 @@
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.6">
+        <v>345</v>
+      </c>
+      <c r="H17" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L17">
+        <f t="shared" si="2"/>
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2992,10 +3223,22 @@
         <v>27</v>
       </c>
       <c r="F18" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.6">
+        <v>346</v>
+      </c>
+      <c r="H18" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L18">
+        <f t="shared" si="2"/>
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3012,10 +3255,22 @@
         <v>27</v>
       </c>
       <c r="F19" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.6">
+        <v>347</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L19">
+        <f t="shared" si="2"/>
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3023,7 +3278,7 @@
         <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -3032,10 +3287,22 @@
         <v>27</v>
       </c>
       <c r="F20" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.6">
+        <v>348</v>
+      </c>
+      <c r="H20" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L20">
+        <f t="shared" si="2"/>
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3052,10 +3319,22 @@
         <v>27</v>
       </c>
       <c r="F21" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.6">
+        <v>349</v>
+      </c>
+      <c r="H21" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L21">
+        <f t="shared" si="2"/>
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3063,7 +3342,7 @@
         <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -3072,10 +3351,22 @@
         <v>27</v>
       </c>
       <c r="F22" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.6">
+        <v>350</v>
+      </c>
+      <c r="H22" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L22">
+        <f t="shared" si="2"/>
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3092,10 +3383,22 @@
         <v>27</v>
       </c>
       <c r="F23" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.6">
+        <v>351</v>
+      </c>
+      <c r="H23" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L23">
+        <f t="shared" si="2"/>
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3112,10 +3415,22 @@
         <v>27</v>
       </c>
       <c r="F24" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.6">
+        <v>352</v>
+      </c>
+      <c r="H24" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L24">
+        <f t="shared" si="2"/>
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3123,7 +3438,7 @@
         <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -3132,10 +3447,22 @@
         <v>27</v>
       </c>
       <c r="F25" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.6">
+        <v>353</v>
+      </c>
+      <c r="H25" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L25">
+        <f t="shared" si="2"/>
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3152,10 +3479,22 @@
         <v>27</v>
       </c>
       <c r="F26" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.6">
+        <v>354</v>
+      </c>
+      <c r="H26" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L26">
+        <f t="shared" si="2"/>
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3172,10 +3511,22 @@
         <v>27</v>
       </c>
       <c r="F27" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.6">
+        <v>355</v>
+      </c>
+      <c r="H27" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L27">
+        <f t="shared" si="2"/>
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3192,10 +3543,22 @@
         <v>27</v>
       </c>
       <c r="F28" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.6">
+        <v>356</v>
+      </c>
+      <c r="H28" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L28">
+        <f t="shared" si="2"/>
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3212,10 +3575,22 @@
         <v>27</v>
       </c>
       <c r="F29" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.6">
+        <v>357</v>
+      </c>
+      <c r="H29" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L29">
+        <f t="shared" si="2"/>
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3232,10 +3607,22 @@
         <v>27</v>
       </c>
       <c r="F30" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.6">
+        <v>358</v>
+      </c>
+      <c r="H30" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L30">
+        <f t="shared" si="2"/>
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3243,7 +3630,7 @@
         <v>41</v>
       </c>
       <c r="C31" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D31" t="s">
         <v>21</v>
@@ -3252,10 +3639,22 @@
         <v>27</v>
       </c>
       <c r="F31" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.6">
+        <v>359</v>
+      </c>
+      <c r="H31" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L31">
+        <f t="shared" si="2"/>
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3263,7 +3662,7 @@
         <v>42</v>
       </c>
       <c r="C32" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D32" t="s">
         <v>21</v>
@@ -3272,10 +3671,22 @@
         <v>27</v>
       </c>
       <c r="F32" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.6">
+        <v>360</v>
+      </c>
+      <c r="H32" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L32">
+        <f t="shared" si="2"/>
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3283,7 +3694,7 @@
         <v>43</v>
       </c>
       <c r="C33" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D33" t="s">
         <v>21</v>
@@ -3292,10 +3703,22 @@
         <v>27</v>
       </c>
       <c r="F33" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.6">
+        <v>361</v>
+      </c>
+      <c r="H33" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L33">
+        <f t="shared" si="2"/>
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3303,7 +3726,7 @@
         <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D34" t="s">
         <v>21</v>
@@ -3312,10 +3735,22 @@
         <v>27</v>
       </c>
       <c r="F34" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.6">
+        <v>362</v>
+      </c>
+      <c r="H34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L34">
+        <f t="shared" si="2"/>
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3323,7 +3758,7 @@
         <v>45</v>
       </c>
       <c r="C35" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D35" t="s">
         <v>21</v>
@@ -3332,10 +3767,22 @@
         <v>27</v>
       </c>
       <c r="F35" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.6">
+        <v>363</v>
+      </c>
+      <c r="H35" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L35">
+        <f t="shared" si="2"/>
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3343,7 +3790,7 @@
         <v>46</v>
       </c>
       <c r="C36" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D36" t="s">
         <v>26</v>
@@ -3352,10 +3799,22 @@
         <v>27</v>
       </c>
       <c r="F36" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.6">
+        <v>364</v>
+      </c>
+      <c r="H36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L36">
+        <f t="shared" si="2"/>
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3372,10 +3831,22 @@
         <v>27</v>
       </c>
       <c r="F37" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.6">
+        <v>365</v>
+      </c>
+      <c r="H37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L37">
+        <f t="shared" si="2"/>
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3392,10 +3863,22 @@
         <v>27</v>
       </c>
       <c r="F38" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.6">
+        <v>366</v>
+      </c>
+      <c r="H38" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L38">
+        <f t="shared" si="2"/>
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3412,10 +3895,22 @@
         <v>27</v>
       </c>
       <c r="F39" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.6">
+        <v>367</v>
+      </c>
+      <c r="H39" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L39">
+        <f t="shared" si="2"/>
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3423,19 +3918,34 @@
         <v>50</v>
       </c>
       <c r="C40" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D40" t="s">
         <v>26</v>
       </c>
       <c r="E40" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="F40" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.6">
+        <v>368</v>
+      </c>
+      <c r="H40" t="str">
+        <f t="shared" si="0"/>
+        <v>1039.png</v>
+      </c>
+      <c r="I40" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J40">
+        <v>1</v>
+      </c>
+      <c r="L40">
+        <f t="shared" si="2"/>
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3452,10 +3962,22 @@
         <v>27</v>
       </c>
       <c r="F41" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.6">
+        <v>369</v>
+      </c>
+      <c r="H41" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L41">
+        <f t="shared" si="2"/>
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3472,10 +3994,22 @@
         <v>27</v>
       </c>
       <c r="F42" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.6">
+        <v>370</v>
+      </c>
+      <c r="H42" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L42">
+        <f t="shared" si="2"/>
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3483,7 +4017,7 @@
         <v>53</v>
       </c>
       <c r="C43" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D43" t="s">
         <v>26</v>
@@ -3492,10 +4026,22 @@
         <v>27</v>
       </c>
       <c r="F43" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.6">
+        <v>371</v>
+      </c>
+      <c r="H43" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L43">
+        <f t="shared" si="2"/>
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3512,10 +4058,22 @@
         <v>62</v>
       </c>
       <c r="F44" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.6">
+        <v>372</v>
+      </c>
+      <c r="H44" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L44">
+        <f t="shared" si="2"/>
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3532,10 +4090,22 @@
         <v>62</v>
       </c>
       <c r="F45" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.6">
+        <v>373</v>
+      </c>
+      <c r="H45" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L45">
+        <f t="shared" si="2"/>
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3543,7 +4113,7 @@
         <v>56</v>
       </c>
       <c r="C46" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -3552,10 +4122,25 @@
         <v>62</v>
       </c>
       <c r="F46" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.6">
+        <v>374</v>
+      </c>
+      <c r="H46" t="str">
+        <f t="shared" si="0"/>
+        <v>1045.png</v>
+      </c>
+      <c r="I46" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J46">
+        <v>1</v>
+      </c>
+      <c r="L46">
+        <f t="shared" si="2"/>
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3572,10 +4157,22 @@
         <v>62</v>
       </c>
       <c r="F47" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.6">
+        <v>375</v>
+      </c>
+      <c r="H47" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L47">
+        <f t="shared" si="2"/>
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3583,7 +4180,7 @@
         <v>58</v>
       </c>
       <c r="C48" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -3592,10 +4189,22 @@
         <v>62</v>
       </c>
       <c r="F48" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.6">
+        <v>376</v>
+      </c>
+      <c r="H48" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L48">
+        <f t="shared" si="2"/>
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3603,7 +4212,7 @@
         <v>59</v>
       </c>
       <c r="C49" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -3612,10 +4221,22 @@
         <v>62</v>
       </c>
       <c r="F49" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.6">
+        <v>377</v>
+      </c>
+      <c r="H49" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L49">
+        <f t="shared" si="2"/>
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3632,10 +4253,22 @@
         <v>62</v>
       </c>
       <c r="F50" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.6">
+        <v>378</v>
+      </c>
+      <c r="H50" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L50">
+        <f t="shared" si="2"/>
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3652,10 +4285,22 @@
         <v>62</v>
       </c>
       <c r="F51" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.6">
+        <v>379</v>
+      </c>
+      <c r="H51" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L51">
+        <f t="shared" si="2"/>
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3663,7 +4308,7 @@
         <v>63</v>
       </c>
       <c r="C52" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D52" t="s">
         <v>21</v>
@@ -3672,10 +4317,25 @@
         <v>62</v>
       </c>
       <c r="F52" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.6">
+        <v>380</v>
+      </c>
+      <c r="H52" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I52" t="str">
+        <f t="shared" si="1"/>
+        <v>1051.mp4</v>
+      </c>
+      <c r="K52">
+        <v>1</v>
+      </c>
+      <c r="L52">
+        <f t="shared" si="2"/>
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3692,10 +4352,22 @@
         <v>62</v>
       </c>
       <c r="F53" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.6">
+        <v>381</v>
+      </c>
+      <c r="H53" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L53">
+        <f t="shared" si="2"/>
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3712,10 +4384,22 @@
         <v>62</v>
       </c>
       <c r="F54" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.6">
+        <v>382</v>
+      </c>
+      <c r="H54" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L54">
+        <f t="shared" si="2"/>
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3723,7 +4407,7 @@
         <v>66</v>
       </c>
       <c r="C55" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D55" t="s">
         <v>21</v>
@@ -3732,10 +4416,22 @@
         <v>62</v>
       </c>
       <c r="F55" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.6">
+        <v>383</v>
+      </c>
+      <c r="H55" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I55" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L55">
+        <f t="shared" si="2"/>
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3743,7 +4439,7 @@
         <v>67</v>
       </c>
       <c r="C56" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D56" t="s">
         <v>21</v>
@@ -3752,10 +4448,22 @@
         <v>62</v>
       </c>
       <c r="F56" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.6">
+        <v>384</v>
+      </c>
+      <c r="H56" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I56" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L56">
+        <f t="shared" si="2"/>
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3772,10 +4480,22 @@
         <v>62</v>
       </c>
       <c r="F57" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.6">
+        <v>385</v>
+      </c>
+      <c r="H57" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L57">
+        <f t="shared" si="2"/>
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3783,7 +4503,7 @@
         <v>69</v>
       </c>
       <c r="C58" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D58" t="s">
         <v>21</v>
@@ -3792,10 +4512,25 @@
         <v>62</v>
       </c>
       <c r="F58" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.6">
+        <v>386</v>
+      </c>
+      <c r="H58" t="str">
+        <f t="shared" si="0"/>
+        <v>1057.png</v>
+      </c>
+      <c r="I58" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J58">
+        <v>1</v>
+      </c>
+      <c r="L58">
+        <f t="shared" si="2"/>
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3812,10 +4547,22 @@
         <v>62</v>
       </c>
       <c r="F59" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.6">
+        <v>387</v>
+      </c>
+      <c r="H59" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L59">
+        <f t="shared" si="2"/>
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3832,10 +4579,22 @@
         <v>62</v>
       </c>
       <c r="F60" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.6">
+        <v>388</v>
+      </c>
+      <c r="H60" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L60">
+        <f t="shared" si="2"/>
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3852,10 +4611,22 @@
         <v>62</v>
       </c>
       <c r="F61" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.6">
+        <v>389</v>
+      </c>
+      <c r="H61" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I61" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L61">
+        <f t="shared" si="2"/>
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3863,7 +4634,7 @@
         <v>73</v>
       </c>
       <c r="C62" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D62" t="s">
         <v>21</v>
@@ -3872,10 +4643,22 @@
         <v>62</v>
       </c>
       <c r="F62" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.6">
+        <v>390</v>
+      </c>
+      <c r="H62" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I62" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L62">
+        <f t="shared" si="2"/>
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A63">
         <v>62</v>
       </c>
@@ -3892,10 +4675,22 @@
         <v>62</v>
       </c>
       <c r="F63" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.6">
+        <v>391</v>
+      </c>
+      <c r="H63" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I63" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L63">
+        <f t="shared" si="2"/>
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A64">
         <v>63</v>
       </c>
@@ -3903,7 +4698,7 @@
         <v>75</v>
       </c>
       <c r="C64" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D64" t="s">
         <v>21</v>
@@ -3912,10 +4707,22 @@
         <v>62</v>
       </c>
       <c r="F64" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.6">
+        <v>392</v>
+      </c>
+      <c r="H64" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I64" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L64">
+        <f t="shared" si="2"/>
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A65">
         <v>64</v>
       </c>
@@ -3923,7 +4730,7 @@
         <v>76</v>
       </c>
       <c r="C65" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D65" t="s">
         <v>21</v>
@@ -3932,10 +4739,22 @@
         <v>62</v>
       </c>
       <c r="F65" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.6">
+        <v>393</v>
+      </c>
+      <c r="H65" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I65" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L65">
+        <f t="shared" si="2"/>
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A66">
         <v>65</v>
       </c>
@@ -3952,10 +4771,22 @@
         <v>62</v>
       </c>
       <c r="F66" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.6">
+        <v>394</v>
+      </c>
+      <c r="H66" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I66" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L66">
+        <f t="shared" si="2"/>
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A67">
         <v>66</v>
       </c>
@@ -3972,10 +4803,22 @@
         <v>62</v>
       </c>
       <c r="F67" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.6">
+        <v>395</v>
+      </c>
+      <c r="H67" t="str">
+        <f t="shared" ref="H67:H130" si="3">IF(J67=1,L67&amp;".png","")</f>
+        <v/>
+      </c>
+      <c r="I67" t="str">
+        <f t="shared" ref="I67:I130" si="4">IF(K67=1,L67&amp;".mp4","")</f>
+        <v/>
+      </c>
+      <c r="L67">
+        <f t="shared" ref="L67:L130" si="5">1000+A67</f>
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A68">
         <v>67</v>
       </c>
@@ -3983,7 +4826,7 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D68" t="s">
         <v>26</v>
@@ -3992,10 +4835,22 @@
         <v>62</v>
       </c>
       <c r="F68" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.6">
+        <v>396</v>
+      </c>
+      <c r="H68" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I68" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L68">
+        <f t="shared" si="5"/>
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A69">
         <v>68</v>
       </c>
@@ -4012,10 +4867,22 @@
         <v>62</v>
       </c>
       <c r="F69" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.6">
+        <v>397</v>
+      </c>
+      <c r="H69" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I69" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L69">
+        <f t="shared" si="5"/>
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4032,10 +4899,22 @@
         <v>62</v>
       </c>
       <c r="F70" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.6">
+        <v>398</v>
+      </c>
+      <c r="H70" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I70" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L70">
+        <f t="shared" si="5"/>
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4052,10 +4931,22 @@
         <v>62</v>
       </c>
       <c r="F71" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.6">
+        <v>399</v>
+      </c>
+      <c r="H71" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I71" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L71">
+        <f t="shared" si="5"/>
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4072,10 +4963,22 @@
         <v>62</v>
       </c>
       <c r="F72" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.6">
+        <v>400</v>
+      </c>
+      <c r="H72" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I72" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L72">
+        <f t="shared" si="5"/>
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4083,7 +4986,7 @@
         <v>84</v>
       </c>
       <c r="C73" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D73" t="s">
         <v>26</v>
@@ -4092,10 +4995,22 @@
         <v>62</v>
       </c>
       <c r="F73" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.6">
+        <v>401</v>
+      </c>
+      <c r="H73" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I73" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L73">
+        <f t="shared" si="5"/>
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4112,10 +5027,22 @@
         <v>62</v>
       </c>
       <c r="F74" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.6">
+        <v>402</v>
+      </c>
+      <c r="H74" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I74" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L74">
+        <f t="shared" si="5"/>
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4132,10 +5059,22 @@
         <v>62</v>
       </c>
       <c r="F75" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.6">
+        <v>403</v>
+      </c>
+      <c r="H75" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I75" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L75">
+        <f t="shared" si="5"/>
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A76">
         <v>75</v>
       </c>
@@ -4143,7 +5082,7 @@
         <v>87</v>
       </c>
       <c r="C76" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D76" t="s">
         <v>26</v>
@@ -4152,10 +5091,22 @@
         <v>62</v>
       </c>
       <c r="F76" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.6">
+        <v>404</v>
+      </c>
+      <c r="H76" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I76" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L76">
+        <f t="shared" si="5"/>
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A77">
         <v>76</v>
       </c>
@@ -4163,7 +5114,7 @@
         <v>88</v>
       </c>
       <c r="C77" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
@@ -4172,10 +5123,22 @@
         <v>90</v>
       </c>
       <c r="F77" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.6">
+        <v>405</v>
+      </c>
+      <c r="H77" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I77" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L77">
+        <f t="shared" si="5"/>
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A78">
         <v>77</v>
       </c>
@@ -4192,10 +5155,22 @@
         <v>90</v>
       </c>
       <c r="F78" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.6">
+        <v>406</v>
+      </c>
+      <c r="H78" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I78" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L78">
+        <f t="shared" si="5"/>
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A79">
         <v>78</v>
       </c>
@@ -4203,7 +5178,7 @@
         <v>91</v>
       </c>
       <c r="C79" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D79" t="s">
         <v>7</v>
@@ -4212,10 +5187,22 @@
         <v>90</v>
       </c>
       <c r="F79" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.6">
+        <v>407</v>
+      </c>
+      <c r="H79" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I79" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L79">
+        <f t="shared" si="5"/>
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A80">
         <v>79</v>
       </c>
@@ -4232,10 +5219,22 @@
         <v>90</v>
       </c>
       <c r="F80" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.6">
+        <v>408</v>
+      </c>
+      <c r="H80" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I80" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L80">
+        <f t="shared" si="5"/>
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A81">
         <v>80</v>
       </c>
@@ -4243,7 +5242,7 @@
         <v>93</v>
       </c>
       <c r="C81" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D81" t="s">
         <v>21</v>
@@ -4252,10 +5251,22 @@
         <v>90</v>
       </c>
       <c r="F81" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.6">
+        <v>409</v>
+      </c>
+      <c r="H81" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I81" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L81">
+        <f t="shared" si="5"/>
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A82">
         <v>81</v>
       </c>
@@ -4263,7 +5274,7 @@
         <v>94</v>
       </c>
       <c r="C82" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D82" t="s">
         <v>21</v>
@@ -4272,10 +5283,22 @@
         <v>90</v>
       </c>
       <c r="F82" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.6">
+        <v>410</v>
+      </c>
+      <c r="H82" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I82" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L82">
+        <f t="shared" si="5"/>
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A83">
         <v>82</v>
       </c>
@@ -4283,7 +5306,7 @@
         <v>95</v>
       </c>
       <c r="C83" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D83" t="s">
         <v>21</v>
@@ -4292,10 +5315,22 @@
         <v>90</v>
       </c>
       <c r="F83" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.6">
+        <v>411</v>
+      </c>
+      <c r="H83" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I83" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L83">
+        <f t="shared" si="5"/>
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A84">
         <v>83</v>
       </c>
@@ -4303,7 +5338,7 @@
         <v>96</v>
       </c>
       <c r="C84" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D84" t="s">
         <v>21</v>
@@ -4312,10 +5347,22 @@
         <v>90</v>
       </c>
       <c r="F84" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.6">
+        <v>412</v>
+      </c>
+      <c r="H84" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I84" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L84">
+        <f t="shared" si="5"/>
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A85">
         <v>84</v>
       </c>
@@ -4332,10 +5379,22 @@
         <v>90</v>
       </c>
       <c r="F85" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.6">
+        <v>413</v>
+      </c>
+      <c r="H85" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I85" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L85">
+        <f t="shared" si="5"/>
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A86">
         <v>85</v>
       </c>
@@ -4352,10 +5411,22 @@
         <v>90</v>
       </c>
       <c r="F86" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.6">
+        <v>414</v>
+      </c>
+      <c r="H86" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I86" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L86">
+        <f t="shared" si="5"/>
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A87">
         <v>86</v>
       </c>
@@ -4363,7 +5434,7 @@
         <v>99</v>
       </c>
       <c r="C87" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D87" t="s">
         <v>26</v>
@@ -4372,10 +5443,22 @@
         <v>90</v>
       </c>
       <c r="F87" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.6">
+        <v>415</v>
+      </c>
+      <c r="H87" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I87" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L87">
+        <f t="shared" si="5"/>
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A88">
         <v>87</v>
       </c>
@@ -4383,7 +5466,7 @@
         <v>100</v>
       </c>
       <c r="C88" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D88" t="s">
         <v>26</v>
@@ -4392,10 +5475,22 @@
         <v>90</v>
       </c>
       <c r="F88" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.6">
+        <v>416</v>
+      </c>
+      <c r="H88" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I88" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L88">
+        <f t="shared" si="5"/>
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A89">
         <v>88</v>
       </c>
@@ -4403,7 +5498,7 @@
         <v>101</v>
       </c>
       <c r="C89" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D89" t="s">
         <v>26</v>
@@ -4412,10 +5507,22 @@
         <v>90</v>
       </c>
       <c r="F89" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.6">
+        <v>417</v>
+      </c>
+      <c r="H89" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I89" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L89">
+        <f t="shared" si="5"/>
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A90">
         <v>89</v>
       </c>
@@ -4432,10 +5539,22 @@
         <v>90</v>
       </c>
       <c r="F90" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.6">
+        <v>418</v>
+      </c>
+      <c r="H90" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I90" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L90">
+        <f t="shared" si="5"/>
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A91">
         <v>90</v>
       </c>
@@ -4452,10 +5571,22 @@
         <v>90</v>
       </c>
       <c r="F91" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.6">
+        <v>419</v>
+      </c>
+      <c r="H91" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I91" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L91">
+        <f t="shared" si="5"/>
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A92">
         <v>91</v>
       </c>
@@ -4463,7 +5594,7 @@
         <v>104</v>
       </c>
       <c r="C92" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D92" t="s">
         <v>26</v>
@@ -4472,10 +5603,22 @@
         <v>90</v>
       </c>
       <c r="F92" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.6">
+        <v>420</v>
+      </c>
+      <c r="H92" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I92" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L92">
+        <f t="shared" si="5"/>
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A93">
         <v>92</v>
       </c>
@@ -4483,7 +5626,7 @@
         <v>105</v>
       </c>
       <c r="C93" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D93" t="s">
         <v>26</v>
@@ -4492,10 +5635,22 @@
         <v>90</v>
       </c>
       <c r="F93" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.6">
+        <v>421</v>
+      </c>
+      <c r="H93" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I93" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L93">
+        <f t="shared" si="5"/>
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A94">
         <v>93</v>
       </c>
@@ -4503,7 +5658,7 @@
         <v>106</v>
       </c>
       <c r="C94" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D94" t="s">
         <v>26</v>
@@ -4512,10 +5667,22 @@
         <v>90</v>
       </c>
       <c r="F94" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.6">
+        <v>422</v>
+      </c>
+      <c r="H94" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I94" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L94">
+        <f t="shared" si="5"/>
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A95">
         <v>94</v>
       </c>
@@ -4523,7 +5690,7 @@
         <v>107</v>
       </c>
       <c r="C95" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D95" t="s">
         <v>26</v>
@@ -4532,10 +5699,22 @@
         <v>90</v>
       </c>
       <c r="F95" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.6">
+        <v>423</v>
+      </c>
+      <c r="H95" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I95" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L95">
+        <f t="shared" si="5"/>
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A96">
         <v>95</v>
       </c>
@@ -4552,10 +5731,22 @@
         <v>90</v>
       </c>
       <c r="F96" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.6">
+        <v>424</v>
+      </c>
+      <c r="H96" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I96" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L96">
+        <f t="shared" si="5"/>
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A97">
         <v>96</v>
       </c>
@@ -4572,10 +5763,22 @@
         <v>90</v>
       </c>
       <c r="F97" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.6">
+        <v>425</v>
+      </c>
+      <c r="H97" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I97" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L97">
+        <f t="shared" si="5"/>
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A98">
         <v>97</v>
       </c>
@@ -4592,10 +5795,22 @@
         <v>110</v>
       </c>
       <c r="F98" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.6">
+        <v>426</v>
+      </c>
+      <c r="H98" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I98" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L98">
+        <f t="shared" si="5"/>
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A99">
         <v>98</v>
       </c>
@@ -4603,7 +5818,7 @@
         <v>112</v>
       </c>
       <c r="C99" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D99" t="s">
         <v>7</v>
@@ -4612,10 +5827,22 @@
         <v>110</v>
       </c>
       <c r="F99" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.6">
+        <v>427</v>
+      </c>
+      <c r="H99" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I99" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L99">
+        <f t="shared" si="5"/>
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A100">
         <v>99</v>
       </c>
@@ -4623,7 +5850,7 @@
         <v>113</v>
       </c>
       <c r="C100" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D100" t="s">
         <v>7</v>
@@ -4632,10 +5859,22 @@
         <v>110</v>
       </c>
       <c r="F100" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.6">
+        <v>428</v>
+      </c>
+      <c r="H100" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I100" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L100">
+        <f t="shared" si="5"/>
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A101">
         <v>100</v>
       </c>
@@ -4652,10 +5891,22 @@
         <v>110</v>
       </c>
       <c r="F101" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.6">
+        <v>429</v>
+      </c>
+      <c r="H101" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I101" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L101">
+        <f t="shared" si="5"/>
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A102">
         <v>101</v>
       </c>
@@ -4672,10 +5923,22 @@
         <v>110</v>
       </c>
       <c r="F102" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.6">
+        <v>430</v>
+      </c>
+      <c r="H102" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I102" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L102">
+        <f t="shared" si="5"/>
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A103">
         <v>102</v>
       </c>
@@ -4683,7 +5946,7 @@
         <v>116</v>
       </c>
       <c r="C103" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D103" t="s">
         <v>21</v>
@@ -4692,10 +5955,22 @@
         <v>110</v>
       </c>
       <c r="F103" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.6">
+        <v>431</v>
+      </c>
+      <c r="H103" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I103" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L103">
+        <f t="shared" si="5"/>
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A104">
         <v>103</v>
       </c>
@@ -4712,10 +5987,22 @@
         <v>110</v>
       </c>
       <c r="F104" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.6">
+        <v>432</v>
+      </c>
+      <c r="H104" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I104" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L104">
+        <f t="shared" si="5"/>
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A105">
         <v>104</v>
       </c>
@@ -4723,7 +6010,7 @@
         <v>117</v>
       </c>
       <c r="C105" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D105" t="s">
         <v>26</v>
@@ -4732,10 +6019,22 @@
         <v>110</v>
       </c>
       <c r="F105" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.6">
+        <v>433</v>
+      </c>
+      <c r="H105" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I105" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L105">
+        <f t="shared" si="5"/>
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A106">
         <v>105</v>
       </c>
@@ -4743,7 +6042,7 @@
         <v>118</v>
       </c>
       <c r="C106" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D106" t="s">
         <v>26</v>
@@ -4752,10 +6051,22 @@
         <v>110</v>
       </c>
       <c r="F106" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.6">
+        <v>434</v>
+      </c>
+      <c r="H106" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I106" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L106">
+        <f t="shared" si="5"/>
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A107">
         <v>106</v>
       </c>
@@ -4763,7 +6074,7 @@
         <v>119</v>
       </c>
       <c r="C107" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D107" t="s">
         <v>26</v>
@@ -4772,18 +6083,30 @@
         <v>110</v>
       </c>
       <c r="F107" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.6">
+        <v>435</v>
+      </c>
+      <c r="H107" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I107" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L107">
+        <f t="shared" si="5"/>
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A108">
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C108" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D108" t="s">
         <v>26</v>
@@ -4792,10 +6115,22 @@
         <v>110</v>
       </c>
       <c r="F108" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.6">
+        <v>436</v>
+      </c>
+      <c r="H108" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I108" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L108">
+        <f t="shared" si="5"/>
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A109">
         <v>108</v>
       </c>
@@ -4803,7 +6138,7 @@
         <v>120</v>
       </c>
       <c r="C109" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D109" t="s">
         <v>26</v>
@@ -4812,10 +6147,22 @@
         <v>110</v>
       </c>
       <c r="F109" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.6">
+        <v>437</v>
+      </c>
+      <c r="H109" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I109" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L109">
+        <f t="shared" si="5"/>
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A110">
         <v>109</v>
       </c>
@@ -4823,7 +6170,7 @@
         <v>121</v>
       </c>
       <c r="C110" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D110" t="s">
         <v>26</v>
@@ -4832,10 +6179,22 @@
         <v>110</v>
       </c>
       <c r="F110" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.6">
+        <v>438</v>
+      </c>
+      <c r="H110" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I110" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L110">
+        <f t="shared" si="5"/>
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A111">
         <v>110</v>
       </c>
@@ -4843,7 +6202,7 @@
         <v>122</v>
       </c>
       <c r="C111" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D111" t="s">
         <v>26</v>
@@ -4852,10 +6211,22 @@
         <v>110</v>
       </c>
       <c r="F111" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.6">
+        <v>439</v>
+      </c>
+      <c r="H111" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I111" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L111">
+        <f t="shared" si="5"/>
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A112">
         <v>111</v>
       </c>
@@ -4863,7 +6234,7 @@
         <v>123</v>
       </c>
       <c r="C112" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D112" t="s">
         <v>26</v>
@@ -4872,10 +6243,22 @@
         <v>110</v>
       </c>
       <c r="F112" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.6">
+        <v>440</v>
+      </c>
+      <c r="H112" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I112" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L112">
+        <f t="shared" si="5"/>
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A113">
         <v>112</v>
       </c>
@@ -4883,7 +6266,7 @@
         <v>124</v>
       </c>
       <c r="C113" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
@@ -4892,10 +6275,22 @@
         <v>126</v>
       </c>
       <c r="F113" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.6">
+        <v>441</v>
+      </c>
+      <c r="H113" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I113" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L113">
+        <f t="shared" si="5"/>
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A114">
         <v>113</v>
       </c>
@@ -4912,10 +6307,22 @@
         <v>126</v>
       </c>
       <c r="F114" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.6">
+        <v>442</v>
+      </c>
+      <c r="H114" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I114" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L114">
+        <f t="shared" si="5"/>
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A115">
         <v>114</v>
       </c>
@@ -4923,7 +6330,7 @@
         <v>127</v>
       </c>
       <c r="C115" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D115" t="s">
         <v>21</v>
@@ -4932,10 +6339,22 @@
         <v>126</v>
       </c>
       <c r="F115" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.6">
+        <v>443</v>
+      </c>
+      <c r="H115" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I115" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L115">
+        <f t="shared" si="5"/>
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A116">
         <v>115</v>
       </c>
@@ -4952,10 +6371,22 @@
         <v>126</v>
       </c>
       <c r="F116" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.6">
+        <v>444</v>
+      </c>
+      <c r="H116" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I116" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L116">
+        <f t="shared" si="5"/>
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A117">
         <v>116</v>
       </c>
@@ -4963,7 +6394,7 @@
         <v>129</v>
       </c>
       <c r="C117" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D117" t="s">
         <v>26</v>
@@ -4972,10 +6403,22 @@
         <v>126</v>
       </c>
       <c r="F117" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.6">
+        <v>445</v>
+      </c>
+      <c r="H117" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I117" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L117">
+        <f t="shared" si="5"/>
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A118">
         <v>117</v>
       </c>
@@ -4983,7 +6426,7 @@
         <v>130</v>
       </c>
       <c r="C118" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D118" t="s">
         <v>26</v>
@@ -4992,10 +6435,22 @@
         <v>126</v>
       </c>
       <c r="F118" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.6">
+        <v>446</v>
+      </c>
+      <c r="H118" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I118" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L118">
+        <f t="shared" si="5"/>
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A119">
         <v>118</v>
       </c>
@@ -5003,7 +6458,7 @@
         <v>131</v>
       </c>
       <c r="C119" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D119" t="s">
         <v>26</v>
@@ -5012,10 +6467,22 @@
         <v>126</v>
       </c>
       <c r="F119" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.6">
+        <v>447</v>
+      </c>
+      <c r="H119" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I119" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L119">
+        <f t="shared" si="5"/>
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A120">
         <v>119</v>
       </c>
@@ -5023,7 +6490,7 @@
         <v>132</v>
       </c>
       <c r="C120" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D120" t="s">
         <v>26</v>
@@ -5032,10 +6499,22 @@
         <v>126</v>
       </c>
       <c r="F120" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.6">
+        <v>448</v>
+      </c>
+      <c r="H120" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I120" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L120">
+        <f t="shared" si="5"/>
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A121">
         <v>120</v>
       </c>
@@ -5043,7 +6522,7 @@
         <v>133</v>
       </c>
       <c r="C121" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D121" t="s">
         <v>26</v>
@@ -5052,10 +6531,22 @@
         <v>126</v>
       </c>
       <c r="F121" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.6">
+        <v>449</v>
+      </c>
+      <c r="H121" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I121" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L121">
+        <f t="shared" si="5"/>
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A122">
         <v>121</v>
       </c>
@@ -5063,7 +6554,7 @@
         <v>134</v>
       </c>
       <c r="C122" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D122" t="s">
         <v>7</v>
@@ -5072,10 +6563,22 @@
         <v>137</v>
       </c>
       <c r="F122" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.6">
+        <v>450</v>
+      </c>
+      <c r="H122" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I122" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L122">
+        <f t="shared" si="5"/>
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A123">
         <v>122</v>
       </c>
@@ -5092,10 +6595,22 @@
         <v>137</v>
       </c>
       <c r="F123" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.6">
+        <v>451</v>
+      </c>
+      <c r="H123" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I123" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L123">
+        <f t="shared" si="5"/>
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A124">
         <v>123</v>
       </c>
@@ -5103,7 +6618,7 @@
         <v>136</v>
       </c>
       <c r="C124" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D124" t="s">
         <v>7</v>
@@ -5112,10 +6627,22 @@
         <v>137</v>
       </c>
       <c r="F124" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.6">
+        <v>452</v>
+      </c>
+      <c r="H124" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I124" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L124">
+        <f t="shared" si="5"/>
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A125">
         <v>124</v>
       </c>
@@ -5123,7 +6650,7 @@
         <v>138</v>
       </c>
       <c r="C125" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D125" t="s">
         <v>26</v>
@@ -5132,10 +6659,22 @@
         <v>137</v>
       </c>
       <c r="F125" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.6">
+        <v>453</v>
+      </c>
+      <c r="H125" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I125" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L125">
+        <f t="shared" si="5"/>
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A126">
         <v>125</v>
       </c>
@@ -5143,7 +6682,7 @@
         <v>139</v>
       </c>
       <c r="C126" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D126" t="s">
         <v>26</v>
@@ -5152,10 +6691,22 @@
         <v>137</v>
       </c>
       <c r="F126" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.6">
+        <v>454</v>
+      </c>
+      <c r="H126" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I126" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L126">
+        <f t="shared" si="5"/>
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A127">
         <v>126</v>
       </c>
@@ -5172,10 +6723,22 @@
         <v>137</v>
       </c>
       <c r="F127" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.6">
+        <v>455</v>
+      </c>
+      <c r="H127" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I127" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L127">
+        <f t="shared" si="5"/>
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A128">
         <v>127</v>
       </c>
@@ -5183,7 +6746,7 @@
         <v>141</v>
       </c>
       <c r="C128" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D128" t="s">
         <v>7</v>
@@ -5192,10 +6755,22 @@
         <v>144</v>
       </c>
       <c r="F128" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.6">
+        <v>456</v>
+      </c>
+      <c r="H128" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I128" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L128">
+        <f t="shared" si="5"/>
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A129">
         <v>128</v>
       </c>
@@ -5212,10 +6787,22 @@
         <v>144</v>
       </c>
       <c r="F129" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.6">
+        <v>457</v>
+      </c>
+      <c r="H129" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I129" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L129">
+        <f t="shared" si="5"/>
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A130">
         <v>129</v>
       </c>
@@ -5232,10 +6819,22 @@
         <v>144</v>
       </c>
       <c r="F130" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.6">
+        <v>458</v>
+      </c>
+      <c r="H130" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="I130" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="L130">
+        <f t="shared" si="5"/>
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A131">
         <v>130</v>
       </c>
@@ -5243,7 +6842,7 @@
         <v>145</v>
       </c>
       <c r="C131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D131" t="s">
         <v>21</v>
@@ -5252,10 +6851,22 @@
         <v>144</v>
       </c>
       <c r="F131" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.6">
+        <v>459</v>
+      </c>
+      <c r="H131" t="str">
+        <f t="shared" ref="H131:H194" si="6">IF(J131=1,L131&amp;".png","")</f>
+        <v/>
+      </c>
+      <c r="I131" t="str">
+        <f t="shared" ref="I131:I194" si="7">IF(K131=1,L131&amp;".mp4","")</f>
+        <v/>
+      </c>
+      <c r="L131">
+        <f t="shared" ref="L131:L194" si="8">1000+A131</f>
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A132">
         <v>131</v>
       </c>
@@ -5272,10 +6883,22 @@
         <v>144</v>
       </c>
       <c r="F132" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.6">
+        <v>460</v>
+      </c>
+      <c r="H132" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I132" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L132">
+        <f t="shared" si="8"/>
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A133">
         <v>132</v>
       </c>
@@ -5292,10 +6915,22 @@
         <v>144</v>
       </c>
       <c r="F133" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.6">
+        <v>461</v>
+      </c>
+      <c r="H133" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I133" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L133">
+        <f t="shared" si="8"/>
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A134">
         <v>133</v>
       </c>
@@ -5303,7 +6938,7 @@
         <v>148</v>
       </c>
       <c r="C134" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D134" t="s">
         <v>21</v>
@@ -5312,10 +6947,22 @@
         <v>144</v>
       </c>
       <c r="F134" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.6">
+        <v>462</v>
+      </c>
+      <c r="H134" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I134" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L134">
+        <f t="shared" si="8"/>
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A135">
         <v>134</v>
       </c>
@@ -5332,10 +6979,22 @@
         <v>144</v>
       </c>
       <c r="F135" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.6">
+        <v>463</v>
+      </c>
+      <c r="H135" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I135" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L135">
+        <f t="shared" si="8"/>
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A136">
         <v>135</v>
       </c>
@@ -5352,15 +7011,27 @@
         <v>144</v>
       </c>
       <c r="F136" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.6">
+        <v>464</v>
+      </c>
+      <c r="H136" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I136" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L136">
+        <f t="shared" si="8"/>
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A137">
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C137" t="s">
         <v>10</v>
@@ -5372,10 +7043,22 @@
         <v>144</v>
       </c>
       <c r="F137" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.6">
+        <v>465</v>
+      </c>
+      <c r="H137" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I137" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L137">
+        <f t="shared" si="8"/>
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A138">
         <v>137</v>
       </c>
@@ -5383,7 +7066,7 @@
         <v>151</v>
       </c>
       <c r="C138" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D138" t="s">
         <v>26</v>
@@ -5392,10 +7075,22 @@
         <v>144</v>
       </c>
       <c r="F138" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.6">
+        <v>466</v>
+      </c>
+      <c r="H138" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I138" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L138">
+        <f t="shared" si="8"/>
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A139">
         <v>138</v>
       </c>
@@ -5412,10 +7107,22 @@
         <v>172</v>
       </c>
       <c r="F139" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.6">
+        <v>467</v>
+      </c>
+      <c r="H139" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I139" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L139">
+        <f t="shared" si="8"/>
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A140">
         <v>139</v>
       </c>
@@ -5432,10 +7139,22 @@
         <v>172</v>
       </c>
       <c r="F140" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.6">
+        <v>468</v>
+      </c>
+      <c r="H140" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I140" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L140">
+        <f t="shared" si="8"/>
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A141">
         <v>140</v>
       </c>
@@ -5452,10 +7171,22 @@
         <v>172</v>
       </c>
       <c r="F141" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.6">
+        <v>469</v>
+      </c>
+      <c r="H141" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I141" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L141">
+        <f t="shared" si="8"/>
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A142">
         <v>141</v>
       </c>
@@ -5463,7 +7194,7 @@
         <v>155</v>
       </c>
       <c r="C142" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
@@ -5472,10 +7203,22 @@
         <v>172</v>
       </c>
       <c r="F142" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.6">
+        <v>470</v>
+      </c>
+      <c r="H142" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I142" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L142">
+        <f t="shared" si="8"/>
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A143">
         <v>142</v>
       </c>
@@ -5492,10 +7235,22 @@
         <v>172</v>
       </c>
       <c r="F143" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.6">
+        <v>471</v>
+      </c>
+      <c r="H143" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I143" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L143">
+        <f t="shared" si="8"/>
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A144">
         <v>143</v>
       </c>
@@ -5512,10 +7267,22 @@
         <v>172</v>
       </c>
       <c r="F144" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.6">
+        <v>472</v>
+      </c>
+      <c r="H144" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I144" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L144">
+        <f t="shared" si="8"/>
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A145">
         <v>144</v>
       </c>
@@ -5532,10 +7299,22 @@
         <v>172</v>
       </c>
       <c r="F145" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.6">
+        <v>473</v>
+      </c>
+      <c r="H145" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I145" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L145">
+        <f t="shared" si="8"/>
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A146">
         <v>145</v>
       </c>
@@ -5543,7 +7322,7 @@
         <v>159</v>
       </c>
       <c r="C146" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D146" t="s">
         <v>21</v>
@@ -5552,10 +7331,22 @@
         <v>172</v>
       </c>
       <c r="F146" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.6">
+        <v>474</v>
+      </c>
+      <c r="H146" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I146" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L146">
+        <f t="shared" si="8"/>
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A147">
         <v>146</v>
       </c>
@@ -5563,7 +7354,7 @@
         <v>160</v>
       </c>
       <c r="C147" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D147" t="s">
         <v>21</v>
@@ -5572,10 +7363,22 @@
         <v>172</v>
       </c>
       <c r="F147" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.6">
+        <v>475</v>
+      </c>
+      <c r="H147" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I147" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L147">
+        <f t="shared" si="8"/>
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A148">
         <v>147</v>
       </c>
@@ -5592,10 +7395,22 @@
         <v>172</v>
       </c>
       <c r="F148" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.6">
+        <v>476</v>
+      </c>
+      <c r="H148" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I148" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L148">
+        <f t="shared" si="8"/>
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A149">
         <v>148</v>
       </c>
@@ -5612,10 +7427,22 @@
         <v>172</v>
       </c>
       <c r="F149" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.6">
+        <v>477</v>
+      </c>
+      <c r="H149" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I149" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L149">
+        <f t="shared" si="8"/>
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A150">
         <v>149</v>
       </c>
@@ -5632,10 +7459,22 @@
         <v>172</v>
       </c>
       <c r="F150" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.6">
+        <v>478</v>
+      </c>
+      <c r="H150" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I150" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L150">
+        <f t="shared" si="8"/>
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A151">
         <v>150</v>
       </c>
@@ -5652,10 +7491,22 @@
         <v>172</v>
       </c>
       <c r="F151" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.6">
+        <v>479</v>
+      </c>
+      <c r="H151" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I151" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L151">
+        <f t="shared" si="8"/>
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A152">
         <v>151</v>
       </c>
@@ -5663,7 +7514,7 @@
         <v>165</v>
       </c>
       <c r="C152" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D152" t="s">
         <v>26</v>
@@ -5672,10 +7523,25 @@
         <v>172</v>
       </c>
       <c r="F152" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.6">
+        <v>480</v>
+      </c>
+      <c r="H152" t="str">
+        <f t="shared" si="6"/>
+        <v>1151.png</v>
+      </c>
+      <c r="I152" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="J152">
+        <v>1</v>
+      </c>
+      <c r="L152">
+        <f t="shared" si="8"/>
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A153">
         <v>152</v>
       </c>
@@ -5683,7 +7549,7 @@
         <v>166</v>
       </c>
       <c r="C153" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D153" t="s">
         <v>26</v>
@@ -5692,10 +7558,22 @@
         <v>172</v>
       </c>
       <c r="F153" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.6">
+        <v>481</v>
+      </c>
+      <c r="H153" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I153" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L153">
+        <f t="shared" si="8"/>
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A154">
         <v>153</v>
       </c>
@@ -5703,7 +7581,7 @@
         <v>167</v>
       </c>
       <c r="C154" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D154" t="s">
         <v>26</v>
@@ -5712,10 +7590,22 @@
         <v>172</v>
       </c>
       <c r="F154" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.6">
+        <v>482</v>
+      </c>
+      <c r="H154" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I154" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L154">
+        <f t="shared" si="8"/>
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A155">
         <v>154</v>
       </c>
@@ -5732,10 +7622,22 @@
         <v>172</v>
       </c>
       <c r="F155" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.6">
+        <v>483</v>
+      </c>
+      <c r="H155" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I155" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L155">
+        <f t="shared" si="8"/>
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A156">
         <v>155</v>
       </c>
@@ -5743,7 +7645,7 @@
         <v>169</v>
       </c>
       <c r="C156" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D156" t="s">
         <v>26</v>
@@ -5752,10 +7654,22 @@
         <v>172</v>
       </c>
       <c r="F156" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.6">
+        <v>484</v>
+      </c>
+      <c r="H156" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I156" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L156">
+        <f t="shared" si="8"/>
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A157">
         <v>156</v>
       </c>
@@ -5763,7 +7677,7 @@
         <v>170</v>
       </c>
       <c r="C157" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D157" t="s">
         <v>26</v>
@@ -5772,10 +7686,22 @@
         <v>172</v>
       </c>
       <c r="F157" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.6">
+        <v>485</v>
+      </c>
+      <c r="H157" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I157" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L157">
+        <f t="shared" si="8"/>
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A158">
         <v>157</v>
       </c>
@@ -5792,10 +7718,22 @@
         <v>172</v>
       </c>
       <c r="F158" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.6">
+        <v>486</v>
+      </c>
+      <c r="H158" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I158" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L158">
+        <f t="shared" si="8"/>
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A159">
         <v>158</v>
       </c>
@@ -5812,10 +7750,22 @@
         <v>184</v>
       </c>
       <c r="F159" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.6">
+        <v>487</v>
+      </c>
+      <c r="H159" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I159" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L159">
+        <f t="shared" si="8"/>
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A160">
         <v>159</v>
       </c>
@@ -5832,10 +7782,22 @@
         <v>184</v>
       </c>
       <c r="F160" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.6">
+        <v>488</v>
+      </c>
+      <c r="H160" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I160" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L160">
+        <f t="shared" si="8"/>
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A161">
         <v>160</v>
       </c>
@@ -5843,7 +7805,7 @@
         <v>175</v>
       </c>
       <c r="C161" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -5852,10 +7814,22 @@
         <v>184</v>
       </c>
       <c r="F161" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.6">
+        <v>489</v>
+      </c>
+      <c r="H161" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I161" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L161">
+        <f t="shared" si="8"/>
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A162">
         <v>161</v>
       </c>
@@ -5863,7 +7837,7 @@
         <v>176</v>
       </c>
       <c r="C162" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D162" t="s">
         <v>21</v>
@@ -5872,10 +7846,22 @@
         <v>184</v>
       </c>
       <c r="F162" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.6">
+        <v>490</v>
+      </c>
+      <c r="H162" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I162" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L162">
+        <f t="shared" si="8"/>
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A163">
         <v>162</v>
       </c>
@@ -5883,7 +7869,7 @@
         <v>177</v>
       </c>
       <c r="C163" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D163" t="s">
         <v>21</v>
@@ -5892,10 +7878,22 @@
         <v>184</v>
       </c>
       <c r="F163" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.6">
+        <v>491</v>
+      </c>
+      <c r="H163" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I163" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L163">
+        <f t="shared" si="8"/>
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A164">
         <v>163</v>
       </c>
@@ -5903,7 +7901,7 @@
         <v>178</v>
       </c>
       <c r="C164" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D164" t="s">
         <v>21</v>
@@ -5912,10 +7910,22 @@
         <v>184</v>
       </c>
       <c r="F164" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.6">
+        <v>492</v>
+      </c>
+      <c r="H164" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I164" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L164">
+        <f t="shared" si="8"/>
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A165">
         <v>164</v>
       </c>
@@ -5923,7 +7933,7 @@
         <v>179</v>
       </c>
       <c r="C165" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D165" t="s">
         <v>21</v>
@@ -5932,10 +7942,22 @@
         <v>184</v>
       </c>
       <c r="F165" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.6">
+        <v>493</v>
+      </c>
+      <c r="H165" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I165" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L165">
+        <f t="shared" si="8"/>
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A166">
         <v>165</v>
       </c>
@@ -5952,10 +7974,22 @@
         <v>184</v>
       </c>
       <c r="F166" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.6">
+        <v>494</v>
+      </c>
+      <c r="H166" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I166" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L166">
+        <f t="shared" si="8"/>
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A167">
         <v>166</v>
       </c>
@@ -5972,10 +8006,22 @@
         <v>184</v>
       </c>
       <c r="F167" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.6">
+        <v>495</v>
+      </c>
+      <c r="H167" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I167" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L167">
+        <f t="shared" si="8"/>
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A168">
         <v>167</v>
       </c>
@@ -5983,7 +8029,7 @@
         <v>182</v>
       </c>
       <c r="C168" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D168" t="s">
         <v>21</v>
@@ -5992,10 +8038,22 @@
         <v>184</v>
       </c>
       <c r="F168" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.6">
+        <v>496</v>
+      </c>
+      <c r="H168" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I168" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L168">
+        <f t="shared" si="8"/>
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A169">
         <v>168</v>
       </c>
@@ -6003,7 +8061,7 @@
         <v>183</v>
       </c>
       <c r="C169" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D169" t="s">
         <v>21</v>
@@ -6012,10 +8070,22 @@
         <v>184</v>
       </c>
       <c r="F169" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.6">
+        <v>497</v>
+      </c>
+      <c r="H169" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I169" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L169">
+        <f t="shared" si="8"/>
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A170">
         <v>169</v>
       </c>
@@ -6023,7 +8093,7 @@
         <v>185</v>
       </c>
       <c r="C170" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D170" t="s">
         <v>26</v>
@@ -6032,10 +8102,22 @@
         <v>184</v>
       </c>
       <c r="F170" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.6">
+        <v>498</v>
+      </c>
+      <c r="H170" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I170" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L170">
+        <f t="shared" si="8"/>
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A171">
         <v>170</v>
       </c>
@@ -6043,7 +8125,7 @@
         <v>186</v>
       </c>
       <c r="C171" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D171" t="s">
         <v>26</v>
@@ -6052,10 +8134,22 @@
         <v>184</v>
       </c>
       <c r="F171" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.6">
+        <v>499</v>
+      </c>
+      <c r="H171" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I171" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L171">
+        <f t="shared" si="8"/>
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A172">
         <v>171</v>
       </c>
@@ -6072,10 +8166,22 @@
         <v>184</v>
       </c>
       <c r="F172" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.6">
+        <v>500</v>
+      </c>
+      <c r="H172" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I172" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L172">
+        <f t="shared" si="8"/>
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A173">
         <v>172</v>
       </c>
@@ -6083,7 +8189,7 @@
         <v>188</v>
       </c>
       <c r="C173" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D173" t="s">
         <v>26</v>
@@ -6092,10 +8198,22 @@
         <v>184</v>
       </c>
       <c r="F173" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.6">
+        <v>501</v>
+      </c>
+      <c r="H173" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I173" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L173">
+        <f t="shared" si="8"/>
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A174">
         <v>173</v>
       </c>
@@ -6112,10 +8230,22 @@
         <v>184</v>
       </c>
       <c r="F174" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.6">
+        <v>502</v>
+      </c>
+      <c r="H174" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I174" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L174">
+        <f t="shared" si="8"/>
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A175">
         <v>174</v>
       </c>
@@ -6123,7 +8253,7 @@
         <v>190</v>
       </c>
       <c r="C175" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -6132,10 +8262,22 @@
         <v>199</v>
       </c>
       <c r="F175" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.6">
+        <v>503</v>
+      </c>
+      <c r="H175" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I175" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L175">
+        <f t="shared" si="8"/>
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A176">
         <v>175</v>
       </c>
@@ -6152,10 +8294,22 @@
         <v>199</v>
       </c>
       <c r="F176" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.6">
+        <v>504</v>
+      </c>
+      <c r="H176" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I176" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L176">
+        <f t="shared" si="8"/>
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A177">
         <v>176</v>
       </c>
@@ -6163,7 +8317,7 @@
         <v>192</v>
       </c>
       <c r="C177" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -6172,10 +8326,22 @@
         <v>199</v>
       </c>
       <c r="F177" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.6">
+        <v>505</v>
+      </c>
+      <c r="H177" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I177" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L177">
+        <f t="shared" si="8"/>
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A178">
         <v>177</v>
       </c>
@@ -6183,7 +8349,7 @@
         <v>193</v>
       </c>
       <c r="C178" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -6192,10 +8358,22 @@
         <v>199</v>
       </c>
       <c r="F178" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.6">
+        <v>506</v>
+      </c>
+      <c r="H178" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I178" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L178">
+        <f t="shared" si="8"/>
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A179">
         <v>178</v>
       </c>
@@ -6203,7 +8381,7 @@
         <v>194</v>
       </c>
       <c r="C179" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
@@ -6212,10 +8390,22 @@
         <v>199</v>
       </c>
       <c r="F179" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.6">
+        <v>507</v>
+      </c>
+      <c r="H179" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I179" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L179">
+        <f t="shared" si="8"/>
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A180">
         <v>179</v>
       </c>
@@ -6223,7 +8413,7 @@
         <v>195</v>
       </c>
       <c r="C180" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -6232,10 +8422,22 @@
         <v>199</v>
       </c>
       <c r="F180" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.6">
+        <v>508</v>
+      </c>
+      <c r="H180" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I180" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L180">
+        <f t="shared" si="8"/>
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A181">
         <v>180</v>
       </c>
@@ -6243,7 +8445,7 @@
         <v>196</v>
       </c>
       <c r="C181" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -6252,10 +8454,22 @@
         <v>199</v>
       </c>
       <c r="F181" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.6">
+        <v>509</v>
+      </c>
+      <c r="H181" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I181" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L181">
+        <f t="shared" si="8"/>
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A182">
         <v>181</v>
       </c>
@@ -6272,10 +8486,22 @@
         <v>199</v>
       </c>
       <c r="F182" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.6">
+        <v>510</v>
+      </c>
+      <c r="H182" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I182" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L182">
+        <f t="shared" si="8"/>
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A183">
         <v>182</v>
       </c>
@@ -6292,10 +8518,22 @@
         <v>199</v>
       </c>
       <c r="F183" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.6">
+        <v>511</v>
+      </c>
+      <c r="H183" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I183" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L183">
+        <f t="shared" si="8"/>
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A184">
         <v>183</v>
       </c>
@@ -6303,7 +8541,7 @@
         <v>200</v>
       </c>
       <c r="C184" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D184" t="s">
         <v>21</v>
@@ -6312,10 +8550,22 @@
         <v>199</v>
       </c>
       <c r="F184" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.6">
+        <v>512</v>
+      </c>
+      <c r="H184" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I184" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L184">
+        <f t="shared" si="8"/>
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A185">
         <v>184</v>
       </c>
@@ -6332,10 +8582,22 @@
         <v>199</v>
       </c>
       <c r="F185" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.6">
+        <v>513</v>
+      </c>
+      <c r="H185" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I185" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L185">
+        <f t="shared" si="8"/>
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A186">
         <v>185</v>
       </c>
@@ -6352,10 +8614,22 @@
         <v>199</v>
       </c>
       <c r="F186" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.6">
+        <v>514</v>
+      </c>
+      <c r="H186" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I186" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L186">
+        <f t="shared" si="8"/>
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A187">
         <v>186</v>
       </c>
@@ -6363,7 +8637,7 @@
         <v>203</v>
       </c>
       <c r="C187" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D187" t="s">
         <v>21</v>
@@ -6372,10 +8646,22 @@
         <v>199</v>
       </c>
       <c r="F187" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.6">
+        <v>515</v>
+      </c>
+      <c r="H187" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I187" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L187">
+        <f t="shared" si="8"/>
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A188">
         <v>187</v>
       </c>
@@ -6383,7 +8669,7 @@
         <v>204</v>
       </c>
       <c r="C188" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D188" t="s">
         <v>21</v>
@@ -6392,10 +8678,22 @@
         <v>199</v>
       </c>
       <c r="F188" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.6">
+        <v>516</v>
+      </c>
+      <c r="H188" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I188" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L188">
+        <f t="shared" si="8"/>
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A189">
         <v>188</v>
       </c>
@@ -6403,7 +8701,7 @@
         <v>205</v>
       </c>
       <c r="C189" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D189" t="s">
         <v>21</v>
@@ -6412,10 +8710,22 @@
         <v>199</v>
       </c>
       <c r="F189" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.6">
+        <v>517</v>
+      </c>
+      <c r="H189" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I189" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L189">
+        <f t="shared" si="8"/>
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A190">
         <v>189</v>
       </c>
@@ -6423,7 +8733,7 @@
         <v>206</v>
       </c>
       <c r="C190" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D190" t="s">
         <v>21</v>
@@ -6432,10 +8742,22 @@
         <v>199</v>
       </c>
       <c r="F190" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.6">
+        <v>518</v>
+      </c>
+      <c r="H190" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I190" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L190">
+        <f t="shared" si="8"/>
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A191">
         <v>190</v>
       </c>
@@ -6443,7 +8765,7 @@
         <v>207</v>
       </c>
       <c r="C191" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D191" t="s">
         <v>26</v>
@@ -6452,10 +8774,22 @@
         <v>199</v>
       </c>
       <c r="F191" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.6">
+        <v>519</v>
+      </c>
+      <c r="H191" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I191" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L191">
+        <f t="shared" si="8"/>
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A192">
         <v>191</v>
       </c>
@@ -6463,7 +8797,7 @@
         <v>208</v>
       </c>
       <c r="C192" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D192" t="s">
         <v>26</v>
@@ -6472,10 +8806,22 @@
         <v>199</v>
       </c>
       <c r="F192" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.6">
+        <v>520</v>
+      </c>
+      <c r="H192" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I192" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L192">
+        <f t="shared" si="8"/>
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A193">
         <v>192</v>
       </c>
@@ -6492,10 +8838,22 @@
         <v>199</v>
       </c>
       <c r="F193" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.6">
+        <v>521</v>
+      </c>
+      <c r="H193" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I193" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L193">
+        <f t="shared" si="8"/>
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A194">
         <v>193</v>
       </c>
@@ -6503,7 +8861,7 @@
         <v>210</v>
       </c>
       <c r="C194" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D194" t="s">
         <v>26</v>
@@ -6512,10 +8870,22 @@
         <v>199</v>
       </c>
       <c r="F194" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.6">
+        <v>522</v>
+      </c>
+      <c r="H194" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="I194" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="L194">
+        <f t="shared" si="8"/>
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A195">
         <v>194</v>
       </c>
@@ -6523,7 +8893,7 @@
         <v>211</v>
       </c>
       <c r="C195" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D195" t="s">
         <v>26</v>
@@ -6532,10 +8902,22 @@
         <v>199</v>
       </c>
       <c r="F195" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.6">
+        <v>523</v>
+      </c>
+      <c r="H195" t="str">
+        <f t="shared" ref="H195:H258" si="9">IF(J195=1,L195&amp;".png","")</f>
+        <v/>
+      </c>
+      <c r="I195" t="str">
+        <f t="shared" ref="I195:I258" si="10">IF(K195=1,L195&amp;".mp4","")</f>
+        <v/>
+      </c>
+      <c r="L195">
+        <f t="shared" ref="L195:L258" si="11">1000+A195</f>
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A196">
         <v>195</v>
       </c>
@@ -6543,7 +8925,7 @@
         <v>212</v>
       </c>
       <c r="C196" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D196" t="s">
         <v>26</v>
@@ -6552,10 +8934,22 @@
         <v>199</v>
       </c>
       <c r="F196" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.6">
+        <v>524</v>
+      </c>
+      <c r="H196" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I196" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L196">
+        <f t="shared" si="11"/>
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A197">
         <v>196</v>
       </c>
@@ -6563,7 +8957,7 @@
         <v>213</v>
       </c>
       <c r="C197" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D197" t="s">
         <v>26</v>
@@ -6572,10 +8966,22 @@
         <v>199</v>
       </c>
       <c r="F197" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.6">
+        <v>525</v>
+      </c>
+      <c r="H197" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I197" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L197">
+        <f t="shared" si="11"/>
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A198">
         <v>197</v>
       </c>
@@ -6583,7 +8989,7 @@
         <v>214</v>
       </c>
       <c r="C198" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D198" t="s">
         <v>26</v>
@@ -6592,10 +8998,22 @@
         <v>199</v>
       </c>
       <c r="F198" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.6">
+        <v>526</v>
+      </c>
+      <c r="H198" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I198" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L198">
+        <f t="shared" si="11"/>
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A199">
         <v>198</v>
       </c>
@@ -6612,10 +9030,22 @@
         <v>222</v>
       </c>
       <c r="F199" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.6">
+        <v>527</v>
+      </c>
+      <c r="H199" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I199" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L199">
+        <f t="shared" si="11"/>
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A200">
         <v>199</v>
       </c>
@@ -6632,10 +9062,22 @@
         <v>222</v>
       </c>
       <c r="F200" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.6">
+        <v>528</v>
+      </c>
+      <c r="H200" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I200" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L200">
+        <f t="shared" si="11"/>
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A201">
         <v>200</v>
       </c>
@@ -6652,10 +9094,22 @@
         <v>222</v>
       </c>
       <c r="F201" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.6">
+        <v>529</v>
+      </c>
+      <c r="H201" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I201" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L201">
+        <f t="shared" si="11"/>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A202">
         <v>201</v>
       </c>
@@ -6663,7 +9117,7 @@
         <v>218</v>
       </c>
       <c r="C202" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -6672,10 +9126,22 @@
         <v>222</v>
       </c>
       <c r="F202" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.6">
+        <v>530</v>
+      </c>
+      <c r="H202" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I202" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L202">
+        <f t="shared" si="11"/>
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A203">
         <v>202</v>
       </c>
@@ -6683,7 +9149,7 @@
         <v>219</v>
       </c>
       <c r="C203" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -6692,10 +9158,25 @@
         <v>222</v>
       </c>
       <c r="F203" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.6">
+        <v>531</v>
+      </c>
+      <c r="H203" t="str">
+        <f t="shared" si="9"/>
+        <v>1202.png</v>
+      </c>
+      <c r="I203" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="J203">
+        <v>1</v>
+      </c>
+      <c r="L203">
+        <f t="shared" si="11"/>
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A204">
         <v>203</v>
       </c>
@@ -6712,10 +9193,22 @@
         <v>222</v>
       </c>
       <c r="F204" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.6">
+        <v>532</v>
+      </c>
+      <c r="H204" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I204" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L204">
+        <f t="shared" si="11"/>
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A205">
         <v>204</v>
       </c>
@@ -6732,10 +9225,22 @@
         <v>222</v>
       </c>
       <c r="F205" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.6">
+        <v>533</v>
+      </c>
+      <c r="H205" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I205" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L205">
+        <f t="shared" si="11"/>
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="206" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A206">
         <v>205</v>
       </c>
@@ -6743,7 +9248,7 @@
         <v>223</v>
       </c>
       <c r="C206" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D206" t="s">
         <v>21</v>
@@ -6752,10 +9257,22 @@
         <v>222</v>
       </c>
       <c r="F206" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.6">
+        <v>534</v>
+      </c>
+      <c r="H206" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I206" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L206">
+        <f t="shared" si="11"/>
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A207">
         <v>206</v>
       </c>
@@ -6763,7 +9280,7 @@
         <v>224</v>
       </c>
       <c r="C207" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D207" t="s">
         <v>21</v>
@@ -6772,10 +9289,22 @@
         <v>222</v>
       </c>
       <c r="F207" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.6">
+        <v>535</v>
+      </c>
+      <c r="H207" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I207" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L207">
+        <f t="shared" si="11"/>
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="208" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A208">
         <v>207</v>
       </c>
@@ -6792,10 +9321,22 @@
         <v>222</v>
       </c>
       <c r="F208" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.6">
+        <v>536</v>
+      </c>
+      <c r="H208" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I208" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L208">
+        <f t="shared" si="11"/>
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="209" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A209">
         <v>208</v>
       </c>
@@ -6803,7 +9344,7 @@
         <v>226</v>
       </c>
       <c r="C209" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D209" t="s">
         <v>21</v>
@@ -6812,10 +9353,22 @@
         <v>222</v>
       </c>
       <c r="F209" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.6">
+        <v>537</v>
+      </c>
+      <c r="H209" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I209" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L209">
+        <f t="shared" si="11"/>
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="210" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A210">
         <v>209</v>
       </c>
@@ -6823,7 +9376,7 @@
         <v>227</v>
       </c>
       <c r="C210" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D210" t="s">
         <v>21</v>
@@ -6832,10 +9385,22 @@
         <v>222</v>
       </c>
       <c r="F210" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.6">
+        <v>538</v>
+      </c>
+      <c r="H210" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I210" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L210">
+        <f t="shared" si="11"/>
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="211" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A211">
         <v>210</v>
       </c>
@@ -6852,10 +9417,22 @@
         <v>222</v>
       </c>
       <c r="F211" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.6">
+        <v>539</v>
+      </c>
+      <c r="H211" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I211" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L211">
+        <f t="shared" si="11"/>
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="212" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A212">
         <v>211</v>
       </c>
@@ -6872,10 +9449,22 @@
         <v>222</v>
       </c>
       <c r="F212" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.6">
+        <v>540</v>
+      </c>
+      <c r="H212" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I212" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L212">
+        <f t="shared" si="11"/>
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="213" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A213">
         <v>212</v>
       </c>
@@ -6883,7 +9472,7 @@
         <v>230</v>
       </c>
       <c r="C213" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D213" t="s">
         <v>21</v>
@@ -6892,10 +9481,22 @@
         <v>222</v>
       </c>
       <c r="F213" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.6">
+        <v>541</v>
+      </c>
+      <c r="H213" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I213" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L213">
+        <f t="shared" si="11"/>
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="214" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A214">
         <v>213</v>
       </c>
@@ -6912,10 +9513,22 @@
         <v>222</v>
       </c>
       <c r="F214" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.6">
+        <v>542</v>
+      </c>
+      <c r="H214" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I214" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L214">
+        <f t="shared" si="11"/>
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="215" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A215">
         <v>214</v>
       </c>
@@ -6923,7 +9536,7 @@
         <v>232</v>
       </c>
       <c r="C215" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D215" t="s">
         <v>21</v>
@@ -6932,10 +9545,22 @@
         <v>222</v>
       </c>
       <c r="F215" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.6">
+        <v>543</v>
+      </c>
+      <c r="H215" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I215" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L215">
+        <f t="shared" si="11"/>
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="216" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A216">
         <v>215</v>
       </c>
@@ -6952,10 +9577,22 @@
         <v>222</v>
       </c>
       <c r="F216" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.6">
+        <v>544</v>
+      </c>
+      <c r="H216" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I216" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L216">
+        <f t="shared" si="11"/>
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="217" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A217">
         <v>216</v>
       </c>
@@ -6963,7 +9600,7 @@
         <v>234</v>
       </c>
       <c r="C217" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D217" t="s">
         <v>26</v>
@@ -6972,10 +9609,22 @@
         <v>222</v>
       </c>
       <c r="F217" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.6">
+        <v>545</v>
+      </c>
+      <c r="H217" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I217" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L217">
+        <f t="shared" si="11"/>
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="218" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A218">
         <v>217</v>
       </c>
@@ -6983,7 +9632,7 @@
         <v>235</v>
       </c>
       <c r="C218" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D218" t="s">
         <v>26</v>
@@ -6992,10 +9641,22 @@
         <v>222</v>
       </c>
       <c r="F218" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.6">
+        <v>546</v>
+      </c>
+      <c r="H218" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I218" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L218">
+        <f t="shared" si="11"/>
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="219" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A219">
         <v>218</v>
       </c>
@@ -7003,7 +9664,7 @@
         <v>236</v>
       </c>
       <c r="C219" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D219" t="s">
         <v>26</v>
@@ -7012,10 +9673,22 @@
         <v>222</v>
       </c>
       <c r="F219" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.6">
+        <v>547</v>
+      </c>
+      <c r="H219" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I219" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L219">
+        <f t="shared" si="11"/>
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="220" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A220">
         <v>219</v>
       </c>
@@ -7032,10 +9705,22 @@
         <v>222</v>
       </c>
       <c r="F220" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.6">
+        <v>548</v>
+      </c>
+      <c r="H220" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I220" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L220">
+        <f t="shared" si="11"/>
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="221" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A221">
         <v>220</v>
       </c>
@@ -7052,10 +9737,22 @@
         <v>222</v>
       </c>
       <c r="F221" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.6">
+        <v>549</v>
+      </c>
+      <c r="H221" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I221" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L221">
+        <f t="shared" si="11"/>
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="222" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A222">
         <v>221</v>
       </c>
@@ -7063,7 +9760,7 @@
         <v>239</v>
       </c>
       <c r="C222" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D222" t="s">
         <v>26</v>
@@ -7072,10 +9769,22 @@
         <v>222</v>
       </c>
       <c r="F222" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.6">
+        <v>550</v>
+      </c>
+      <c r="H222" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I222" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L222">
+        <f t="shared" si="11"/>
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="223" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A223">
         <v>222</v>
       </c>
@@ -7092,10 +9801,22 @@
         <v>222</v>
       </c>
       <c r="F223" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.6">
+        <v>551</v>
+      </c>
+      <c r="H223" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I223" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L223">
+        <f t="shared" si="11"/>
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="224" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A224">
         <v>223</v>
       </c>
@@ -7112,10 +9833,22 @@
         <v>251</v>
       </c>
       <c r="F224" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.6">
+        <v>553</v>
+      </c>
+      <c r="H224" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I224" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L224">
+        <f t="shared" si="11"/>
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A225">
         <v>224</v>
       </c>
@@ -7132,10 +9865,22 @@
         <v>251</v>
       </c>
       <c r="F225" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.6">
+        <v>554</v>
+      </c>
+      <c r="H225" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I225" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L225">
+        <f t="shared" si="11"/>
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A226">
         <v>225</v>
       </c>
@@ -7143,7 +9888,7 @@
         <v>243</v>
       </c>
       <c r="C226" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D226" t="s">
         <v>7</v>
@@ -7152,10 +9897,22 @@
         <v>251</v>
       </c>
       <c r="F226" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.6">
+        <v>555</v>
+      </c>
+      <c r="H226" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I226" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L226">
+        <f t="shared" si="11"/>
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A227">
         <v>226</v>
       </c>
@@ -7172,10 +9929,22 @@
         <v>251</v>
       </c>
       <c r="F227" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.6">
+        <v>556</v>
+      </c>
+      <c r="H227" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I227" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L227">
+        <f t="shared" si="11"/>
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A228">
         <v>227</v>
       </c>
@@ -7192,10 +9961,22 @@
         <v>251</v>
       </c>
       <c r="F228" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.6">
+        <v>557</v>
+      </c>
+      <c r="H228" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I228" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L228">
+        <f t="shared" si="11"/>
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A229">
         <v>228</v>
       </c>
@@ -7203,7 +9984,7 @@
         <v>246</v>
       </c>
       <c r="C229" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D229" t="s">
         <v>7</v>
@@ -7212,10 +9993,22 @@
         <v>251</v>
       </c>
       <c r="F229" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.6">
+        <v>558</v>
+      </c>
+      <c r="H229" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I229" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L229">
+        <f t="shared" si="11"/>
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A230">
         <v>229</v>
       </c>
@@ -7223,7 +10016,7 @@
         <v>247</v>
       </c>
       <c r="C230" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
@@ -7232,10 +10025,22 @@
         <v>251</v>
       </c>
       <c r="F230" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.6">
+        <v>559</v>
+      </c>
+      <c r="H230" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I230" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L230">
+        <f t="shared" si="11"/>
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A231">
         <v>230</v>
       </c>
@@ -7252,10 +10057,22 @@
         <v>251</v>
       </c>
       <c r="F231" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.6">
+        <v>560</v>
+      </c>
+      <c r="H231" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I231" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L231">
+        <f t="shared" si="11"/>
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A232">
         <v>231</v>
       </c>
@@ -7263,7 +10080,7 @@
         <v>249</v>
       </c>
       <c r="C232" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D232" t="s">
         <v>7</v>
@@ -7272,10 +10089,22 @@
         <v>251</v>
       </c>
       <c r="F232" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.6">
+        <v>561</v>
+      </c>
+      <c r="H232" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I232" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L232">
+        <f t="shared" si="11"/>
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="233" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A233">
         <v>233</v>
       </c>
@@ -7292,10 +10121,22 @@
         <v>251</v>
       </c>
       <c r="F233" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.6">
+        <v>562</v>
+      </c>
+      <c r="H233" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I233" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L233">
+        <f t="shared" si="11"/>
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="234" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A234">
         <v>234</v>
       </c>
@@ -7303,7 +10144,7 @@
         <v>252</v>
       </c>
       <c r="C234" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D234" t="s">
         <v>21</v>
@@ -7312,10 +10153,22 @@
         <v>251</v>
       </c>
       <c r="F234" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.6">
+        <v>563</v>
+      </c>
+      <c r="H234" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I234" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L234">
+        <f t="shared" si="11"/>
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="235" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A235">
         <v>235</v>
       </c>
@@ -7323,7 +10176,7 @@
         <v>253</v>
       </c>
       <c r="C235" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D235" t="s">
         <v>21</v>
@@ -7332,10 +10185,22 @@
         <v>251</v>
       </c>
       <c r="F235" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.6">
+        <v>564</v>
+      </c>
+      <c r="H235" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I235" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L235">
+        <f t="shared" si="11"/>
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A236">
         <v>236</v>
       </c>
@@ -7343,7 +10208,7 @@
         <v>254</v>
       </c>
       <c r="C236" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D236" t="s">
         <v>21</v>
@@ -7352,10 +10217,22 @@
         <v>251</v>
       </c>
       <c r="F236" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.6">
+        <v>565</v>
+      </c>
+      <c r="H236" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I236" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L236">
+        <f t="shared" si="11"/>
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="237" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A237">
         <v>237</v>
       </c>
@@ -7372,10 +10249,22 @@
         <v>251</v>
       </c>
       <c r="F237" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.6">
+        <v>566</v>
+      </c>
+      <c r="H237" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I237" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L237">
+        <f t="shared" si="11"/>
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="238" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A238">
         <v>238</v>
       </c>
@@ -7383,7 +10272,7 @@
         <v>256</v>
       </c>
       <c r="C238" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D238" t="s">
         <v>21</v>
@@ -7392,10 +10281,22 @@
         <v>251</v>
       </c>
       <c r="F238" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.6">
+        <v>567</v>
+      </c>
+      <c r="H238" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I238" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L238">
+        <f t="shared" si="11"/>
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="239" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A239">
         <v>239</v>
       </c>
@@ -7412,10 +10313,22 @@
         <v>251</v>
       </c>
       <c r="F239" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.6">
+        <v>568</v>
+      </c>
+      <c r="H239" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I239" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L239">
+        <f t="shared" si="11"/>
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="240" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A240">
         <v>240</v>
       </c>
@@ -7432,10 +10345,22 @@
         <v>251</v>
       </c>
       <c r="F240" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.6">
+        <v>569</v>
+      </c>
+      <c r="H240" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I240" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L240">
+        <f t="shared" si="11"/>
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="241" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A241">
         <v>241</v>
       </c>
@@ -7443,7 +10368,7 @@
         <v>259</v>
       </c>
       <c r="C241" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D241" t="s">
         <v>21</v>
@@ -7452,10 +10377,22 @@
         <v>251</v>
       </c>
       <c r="F241" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.6">
+        <v>570</v>
+      </c>
+      <c r="H241" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I241" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L241">
+        <f t="shared" si="11"/>
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="242" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A242">
         <v>242</v>
       </c>
@@ -7463,7 +10400,7 @@
         <v>260</v>
       </c>
       <c r="C242" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D242" t="s">
         <v>21</v>
@@ -7472,10 +10409,22 @@
         <v>251</v>
       </c>
       <c r="F242" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.6">
+        <v>571</v>
+      </c>
+      <c r="H242" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I242" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L242">
+        <f t="shared" si="11"/>
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="243" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A243">
         <v>243</v>
       </c>
@@ -7483,7 +10432,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D243" t="s">
         <v>26</v>
@@ -7492,10 +10441,22 @@
         <v>251</v>
       </c>
       <c r="F243" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.6">
+        <v>572</v>
+      </c>
+      <c r="H243" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I243" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L243">
+        <f t="shared" si="11"/>
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="244" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A244">
         <v>244</v>
       </c>
@@ -7503,7 +10464,7 @@
         <v>262</v>
       </c>
       <c r="C244" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D244" t="s">
         <v>26</v>
@@ -7512,10 +10473,22 @@
         <v>251</v>
       </c>
       <c r="F244" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.6">
+        <v>573</v>
+      </c>
+      <c r="H244" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I244" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L244">
+        <f t="shared" si="11"/>
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="245" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A245">
         <v>245</v>
       </c>
@@ -7523,7 +10496,7 @@
         <v>263</v>
       </c>
       <c r="C245" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D245" t="s">
         <v>26</v>
@@ -7532,10 +10505,22 @@
         <v>251</v>
       </c>
       <c r="F245" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.6">
+        <v>574</v>
+      </c>
+      <c r="H245" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I245" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L245">
+        <f t="shared" si="11"/>
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="246" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A246">
         <v>246</v>
       </c>
@@ -7543,7 +10528,7 @@
         <v>264</v>
       </c>
       <c r="C246" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D246" t="s">
         <v>26</v>
@@ -7552,10 +10537,22 @@
         <v>251</v>
       </c>
       <c r="F246" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.6">
+        <v>575</v>
+      </c>
+      <c r="H246" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I246" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L246">
+        <f t="shared" si="11"/>
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="247" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A247">
         <v>247</v>
       </c>
@@ -7572,10 +10569,22 @@
         <v>251</v>
       </c>
       <c r="F247" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.6">
+        <v>576</v>
+      </c>
+      <c r="H247" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I247" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L247">
+        <f t="shared" si="11"/>
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="248" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A248">
         <v>248</v>
       </c>
@@ -7583,7 +10592,7 @@
         <v>266</v>
       </c>
       <c r="C248" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D248" t="s">
         <v>26</v>
@@ -7592,10 +10601,22 @@
         <v>251</v>
       </c>
       <c r="F248" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.6">
+        <v>577</v>
+      </c>
+      <c r="H248" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I248" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L248">
+        <f t="shared" si="11"/>
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="249" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A249">
         <v>249</v>
       </c>
@@ -7603,7 +10624,7 @@
         <v>267</v>
       </c>
       <c r="C249" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D249" t="s">
         <v>26</v>
@@ -7612,10 +10633,22 @@
         <v>251</v>
       </c>
       <c r="F249" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.6">
+        <v>578</v>
+      </c>
+      <c r="H249" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I249" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L249">
+        <f t="shared" si="11"/>
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="250" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A250">
         <v>250</v>
       </c>
@@ -7632,10 +10665,22 @@
         <v>251</v>
       </c>
       <c r="F250" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.6">
+        <v>579</v>
+      </c>
+      <c r="H250" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I250" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L250">
+        <f t="shared" si="11"/>
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="251" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A251">
         <v>251</v>
       </c>
@@ -7643,7 +10688,7 @@
         <v>269</v>
       </c>
       <c r="C251" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D251" t="s">
         <v>26</v>
@@ -7652,10 +10697,22 @@
         <v>251</v>
       </c>
       <c r="F251" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.6">
+        <v>580</v>
+      </c>
+      <c r="H251" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I251" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L251">
+        <f t="shared" si="11"/>
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="252" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A252">
         <v>252</v>
       </c>
@@ -7663,7 +10720,7 @@
         <v>270</v>
       </c>
       <c r="C252" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D252" t="s">
         <v>7</v>
@@ -7672,10 +10729,22 @@
         <v>276</v>
       </c>
       <c r="F252" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.6">
+        <v>581</v>
+      </c>
+      <c r="H252" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I252" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L252">
+        <f t="shared" si="11"/>
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="253" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A253">
         <v>253</v>
       </c>
@@ -7683,7 +10752,7 @@
         <v>271</v>
       </c>
       <c r="C253" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D253" t="s">
         <v>7</v>
@@ -7692,10 +10761,22 @@
         <v>276</v>
       </c>
       <c r="F253" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.6">
+        <v>582</v>
+      </c>
+      <c r="H253" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I253" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L253">
+        <f t="shared" si="11"/>
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="254" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A254">
         <v>254</v>
       </c>
@@ -7712,10 +10793,22 @@
         <v>276</v>
       </c>
       <c r="F254" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.6">
+        <v>583</v>
+      </c>
+      <c r="H254" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I254" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L254">
+        <f t="shared" si="11"/>
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="255" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A255">
         <v>255</v>
       </c>
@@ -7723,7 +10816,7 @@
         <v>273</v>
       </c>
       <c r="C255" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D255" t="s">
         <v>7</v>
@@ -7732,10 +10825,22 @@
         <v>276</v>
       </c>
       <c r="F255" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.6">
+        <v>584</v>
+      </c>
+      <c r="H255" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I255" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L255">
+        <f t="shared" si="11"/>
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="256" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A256">
         <v>256</v>
       </c>
@@ -7743,7 +10848,7 @@
         <v>274</v>
       </c>
       <c r="C256" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D256" t="s">
         <v>7</v>
@@ -7752,10 +10857,25 @@
         <v>276</v>
       </c>
       <c r="F256" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.6">
+        <v>585</v>
+      </c>
+      <c r="H256" t="str">
+        <f t="shared" si="9"/>
+        <v>1256.png</v>
+      </c>
+      <c r="I256" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="J256">
+        <v>1</v>
+      </c>
+      <c r="L256">
+        <f t="shared" si="11"/>
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="257" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A257">
         <v>257</v>
       </c>
@@ -7772,10 +10892,22 @@
         <v>276</v>
       </c>
       <c r="F257" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.6">
+        <v>586</v>
+      </c>
+      <c r="H257" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I257" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L257">
+        <f t="shared" si="11"/>
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="258" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A258">
         <v>258</v>
       </c>
@@ -7792,10 +10924,22 @@
         <v>276</v>
       </c>
       <c r="F258" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.6">
+        <v>587</v>
+      </c>
+      <c r="H258" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="I258" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L258">
+        <f t="shared" si="11"/>
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="259" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A259">
         <v>259</v>
       </c>
@@ -7803,7 +10947,7 @@
         <v>278</v>
       </c>
       <c r="C259" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D259" t="s">
         <v>21</v>
@@ -7812,10 +10956,22 @@
         <v>276</v>
       </c>
       <c r="F259" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.6">
+        <v>588</v>
+      </c>
+      <c r="H259" t="str">
+        <f t="shared" ref="H259:H297" si="12">IF(J259=1,L259&amp;".png","")</f>
+        <v/>
+      </c>
+      <c r="I259" t="str">
+        <f t="shared" ref="I259:I297" si="13">IF(K259=1,L259&amp;".mp4","")</f>
+        <v/>
+      </c>
+      <c r="L259">
+        <f t="shared" ref="L259:L297" si="14">1000+A259</f>
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="260" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A260">
         <v>260</v>
       </c>
@@ -7823,7 +10979,7 @@
         <v>279</v>
       </c>
       <c r="C260" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D260" t="s">
         <v>21</v>
@@ -7832,10 +10988,22 @@
         <v>276</v>
       </c>
       <c r="F260" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.6">
+        <v>589</v>
+      </c>
+      <c r="H260" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I260" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L260">
+        <f t="shared" si="14"/>
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="261" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A261">
         <v>261</v>
       </c>
@@ -7843,7 +11011,7 @@
         <v>280</v>
       </c>
       <c r="C261" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D261" t="s">
         <v>21</v>
@@ -7852,10 +11020,22 @@
         <v>276</v>
       </c>
       <c r="F261" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.6">
+        <v>590</v>
+      </c>
+      <c r="H261" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I261" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L261">
+        <f t="shared" si="14"/>
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="262" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A262">
         <v>262</v>
       </c>
@@ -7863,7 +11043,7 @@
         <v>281</v>
       </c>
       <c r="C262" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D262" t="s">
         <v>21</v>
@@ -7872,10 +11052,22 @@
         <v>276</v>
       </c>
       <c r="F262" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.6">
+        <v>591</v>
+      </c>
+      <c r="H262" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I262" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L262">
+        <f t="shared" si="14"/>
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="263" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A263">
         <v>263</v>
       </c>
@@ -7892,10 +11084,22 @@
         <v>276</v>
       </c>
       <c r="F263" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.6">
+        <v>592</v>
+      </c>
+      <c r="H263" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I263" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L263">
+        <f t="shared" si="14"/>
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="264" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A264">
         <v>264</v>
       </c>
@@ -7903,7 +11107,7 @@
         <v>283</v>
       </c>
       <c r="C264" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D264" t="s">
         <v>21</v>
@@ -7912,10 +11116,22 @@
         <v>276</v>
       </c>
       <c r="F264" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.6">
+        <v>593</v>
+      </c>
+      <c r="H264" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I264" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L264">
+        <f t="shared" si="14"/>
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="265" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A265">
         <v>265</v>
       </c>
@@ -7923,7 +11139,7 @@
         <v>284</v>
       </c>
       <c r="C265" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D265" t="s">
         <v>21</v>
@@ -7932,10 +11148,22 @@
         <v>276</v>
       </c>
       <c r="F265" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.6">
+        <v>594</v>
+      </c>
+      <c r="H265" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I265" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L265">
+        <f t="shared" si="14"/>
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="266" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A266">
         <v>266</v>
       </c>
@@ -7943,7 +11171,7 @@
         <v>285</v>
       </c>
       <c r="C266" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D266" t="s">
         <v>21</v>
@@ -7952,10 +11180,22 @@
         <v>276</v>
       </c>
       <c r="F266" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.6">
+        <v>595</v>
+      </c>
+      <c r="H266" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I266" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L266">
+        <f t="shared" si="14"/>
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="267" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A267">
         <v>267</v>
       </c>
@@ -7963,7 +11203,7 @@
         <v>286</v>
       </c>
       <c r="C267" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D267" t="s">
         <v>21</v>
@@ -7972,10 +11212,22 @@
         <v>276</v>
       </c>
       <c r="F267" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.6">
+        <v>596</v>
+      </c>
+      <c r="H267" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I267" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L267">
+        <f t="shared" si="14"/>
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="268" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A268">
         <v>268</v>
       </c>
@@ -7983,7 +11235,7 @@
         <v>287</v>
       </c>
       <c r="C268" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D268" t="s">
         <v>21</v>
@@ -7992,10 +11244,22 @@
         <v>276</v>
       </c>
       <c r="F268" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.6">
+        <v>597</v>
+      </c>
+      <c r="H268" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I268" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L268">
+        <f t="shared" si="14"/>
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="269" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A269">
         <v>269</v>
       </c>
@@ -8012,10 +11276,22 @@
         <v>276</v>
       </c>
       <c r="F269" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.6">
+        <v>598</v>
+      </c>
+      <c r="H269" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I269" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L269">
+        <f t="shared" si="14"/>
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="270" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A270">
         <v>270</v>
       </c>
@@ -8023,7 +11299,7 @@
         <v>289</v>
       </c>
       <c r="C270" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D270" t="s">
         <v>26</v>
@@ -8032,10 +11308,22 @@
         <v>276</v>
       </c>
       <c r="F270" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.6">
+        <v>599</v>
+      </c>
+      <c r="H270" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I270" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L270">
+        <f t="shared" si="14"/>
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="271" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A271">
         <v>271</v>
       </c>
@@ -8043,7 +11331,7 @@
         <v>290</v>
       </c>
       <c r="C271" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D271" t="s">
         <v>26</v>
@@ -8052,10 +11340,22 @@
         <v>276</v>
       </c>
       <c r="F271" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.6">
+        <v>600</v>
+      </c>
+      <c r="H271" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I271" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L271">
+        <f t="shared" si="14"/>
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="272" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A272">
         <v>272</v>
       </c>
@@ -8063,7 +11363,7 @@
         <v>291</v>
       </c>
       <c r="C272" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D272" t="s">
         <v>26</v>
@@ -8072,10 +11372,22 @@
         <v>276</v>
       </c>
       <c r="F272" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.6">
+        <v>601</v>
+      </c>
+      <c r="H272" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I272" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L272">
+        <f t="shared" si="14"/>
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="273" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A273">
         <v>273</v>
       </c>
@@ -8083,7 +11395,7 @@
         <v>292</v>
       </c>
       <c r="C273" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D273" t="s">
         <v>26</v>
@@ -8092,10 +11404,22 @@
         <v>276</v>
       </c>
       <c r="F273" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.6">
+        <v>602</v>
+      </c>
+      <c r="H273" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I273" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L273">
+        <f t="shared" si="14"/>
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="274" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A274">
         <v>274</v>
       </c>
@@ -8103,7 +11427,7 @@
         <v>293</v>
       </c>
       <c r="C274" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D274" t="s">
         <v>26</v>
@@ -8112,10 +11436,22 @@
         <v>276</v>
       </c>
       <c r="F274" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.6">
+        <v>603</v>
+      </c>
+      <c r="H274" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I274" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L274">
+        <f t="shared" si="14"/>
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="275" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A275">
         <v>275</v>
       </c>
@@ -8123,7 +11459,7 @@
         <v>294</v>
       </c>
       <c r="C275" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D275" t="s">
         <v>26</v>
@@ -8132,10 +11468,22 @@
         <v>276</v>
       </c>
       <c r="F275" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.6">
+        <v>604</v>
+      </c>
+      <c r="H275" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I275" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L275">
+        <f t="shared" si="14"/>
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="276" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A276">
         <v>276</v>
       </c>
@@ -8152,10 +11500,22 @@
         <v>276</v>
       </c>
       <c r="F276" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.6">
+        <v>605</v>
+      </c>
+      <c r="H276" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I276" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L276">
+        <f t="shared" si="14"/>
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="277" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A277">
         <v>277</v>
       </c>
@@ -8163,7 +11523,7 @@
         <v>296</v>
       </c>
       <c r="C277" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D277" t="s">
         <v>26</v>
@@ -8172,10 +11532,22 @@
         <v>276</v>
       </c>
       <c r="F277" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.6">
+        <v>606</v>
+      </c>
+      <c r="H277" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I277" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L277">
+        <f t="shared" si="14"/>
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="278" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A278">
         <v>278</v>
       </c>
@@ -8192,10 +11564,22 @@
         <v>276</v>
       </c>
       <c r="F278" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.6">
+        <v>607</v>
+      </c>
+      <c r="H278" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I278" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L278">
+        <f t="shared" si="14"/>
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="279" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A279">
         <v>279</v>
       </c>
@@ -8203,7 +11587,7 @@
         <v>298</v>
       </c>
       <c r="C279" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D279" t="s">
         <v>26</v>
@@ -8212,10 +11596,22 @@
         <v>276</v>
       </c>
       <c r="F279" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.6">
+        <v>608</v>
+      </c>
+      <c r="H279" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I279" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L279">
+        <f t="shared" si="14"/>
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="280" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A280">
         <v>280</v>
       </c>
@@ -8223,7 +11619,7 @@
         <v>299</v>
       </c>
       <c r="C280" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D280" t="s">
         <v>26</v>
@@ -8232,10 +11628,22 @@
         <v>276</v>
       </c>
       <c r="F280" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.6">
+        <v>609</v>
+      </c>
+      <c r="H280" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I280" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L280">
+        <f t="shared" si="14"/>
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="281" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A281">
         <v>281</v>
       </c>
@@ -8243,7 +11651,7 @@
         <v>300</v>
       </c>
       <c r="C281" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D281" t="s">
         <v>7</v>
@@ -8252,10 +11660,22 @@
         <v>311</v>
       </c>
       <c r="F281" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.6">
+        <v>610</v>
+      </c>
+      <c r="H281" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I281" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L281">
+        <f t="shared" si="14"/>
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="282" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A282">
         <v>282</v>
       </c>
@@ -8263,7 +11683,7 @@
         <v>301</v>
       </c>
       <c r="C282" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D282" t="s">
         <v>7</v>
@@ -8272,10 +11692,22 @@
         <v>311</v>
       </c>
       <c r="F282" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.6">
+        <v>611</v>
+      </c>
+      <c r="H282" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I282" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L282">
+        <f t="shared" si="14"/>
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="283" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A283">
         <v>283</v>
       </c>
@@ -8283,7 +11715,7 @@
         <v>302</v>
       </c>
       <c r="C283" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D283" t="s">
         <v>21</v>
@@ -8292,10 +11724,22 @@
         <v>311</v>
       </c>
       <c r="F283" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.6">
+        <v>612</v>
+      </c>
+      <c r="H283" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I283" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L283">
+        <f t="shared" si="14"/>
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="284" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A284">
         <v>284</v>
       </c>
@@ -8303,7 +11747,7 @@
         <v>303</v>
       </c>
       <c r="C284" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D284" t="s">
         <v>21</v>
@@ -8312,10 +11756,22 @@
         <v>311</v>
       </c>
       <c r="F284" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.6">
+        <v>613</v>
+      </c>
+      <c r="H284" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I284" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L284">
+        <f t="shared" si="14"/>
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="285" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A285">
         <v>285</v>
       </c>
@@ -8323,7 +11779,7 @@
         <v>304</v>
       </c>
       <c r="C285" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D285" t="s">
         <v>21</v>
@@ -8332,10 +11788,22 @@
         <v>311</v>
       </c>
       <c r="F285" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.6">
+        <v>614</v>
+      </c>
+      <c r="H285" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I285" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L285">
+        <f t="shared" si="14"/>
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="286" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A286">
         <v>286</v>
       </c>
@@ -8343,7 +11811,7 @@
         <v>305</v>
       </c>
       <c r="C286" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D286" t="s">
         <v>26</v>
@@ -8352,10 +11820,22 @@
         <v>311</v>
       </c>
       <c r="F286" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.6">
+        <v>615</v>
+      </c>
+      <c r="H286" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I286" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L286">
+        <f t="shared" si="14"/>
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="287" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A287">
         <v>287</v>
       </c>
@@ -8363,7 +11843,7 @@
         <v>306</v>
       </c>
       <c r="C287" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D287" t="s">
         <v>26</v>
@@ -8372,10 +11852,22 @@
         <v>311</v>
       </c>
       <c r="F287" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.6">
+        <v>616</v>
+      </c>
+      <c r="H287" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I287" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L287">
+        <f t="shared" si="14"/>
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="288" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A288">
         <v>288</v>
       </c>
@@ -8383,7 +11875,7 @@
         <v>307</v>
       </c>
       <c r="C288" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D288" t="s">
         <v>26</v>
@@ -8392,10 +11884,22 @@
         <v>311</v>
       </c>
       <c r="F288" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.6">
+        <v>617</v>
+      </c>
+      <c r="H288" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I288" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L288">
+        <f t="shared" si="14"/>
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="289" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A289">
         <v>289</v>
       </c>
@@ -8412,10 +11916,22 @@
         <v>311</v>
       </c>
       <c r="F289" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.6">
+        <v>618</v>
+      </c>
+      <c r="H289" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I289" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L289">
+        <f t="shared" si="14"/>
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="290" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A290">
         <v>290</v>
       </c>
@@ -8423,7 +11939,7 @@
         <v>309</v>
       </c>
       <c r="C290" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D290" t="s">
         <v>26</v>
@@ -8432,10 +11948,22 @@
         <v>311</v>
       </c>
       <c r="F290" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.6">
+        <v>619</v>
+      </c>
+      <c r="H290" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I290" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L290">
+        <f t="shared" si="14"/>
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="291" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A291">
         <v>291</v>
       </c>
@@ -8443,7 +11971,7 @@
         <v>310</v>
       </c>
       <c r="C291" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D291" t="s">
         <v>26</v>
@@ -8452,10 +11980,22 @@
         <v>311</v>
       </c>
       <c r="F291" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.6">
+        <v>620</v>
+      </c>
+      <c r="H291" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I291" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L291">
+        <f t="shared" si="14"/>
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="292" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A292">
         <v>292</v>
       </c>
@@ -8472,10 +12012,22 @@
         <v>90</v>
       </c>
       <c r="F292" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.6">
+        <v>621</v>
+      </c>
+      <c r="H292" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I292" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L292">
+        <f t="shared" si="14"/>
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="293" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A293">
         <v>293</v>
       </c>
@@ -8492,15 +12044,27 @@
         <v>311</v>
       </c>
       <c r="F293" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.6">
+        <v>622</v>
+      </c>
+      <c r="H293" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I293" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L293">
+        <f t="shared" si="14"/>
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="294" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A294">
         <v>294</v>
       </c>
       <c r="B294" t="s">
-        <v>317</v>
+        <v>632</v>
       </c>
       <c r="C294" t="s">
         <v>315</v>
@@ -8512,18 +12076,30 @@
         <v>311</v>
       </c>
       <c r="F294" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.6">
+        <v>623</v>
+      </c>
+      <c r="H294" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I294" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L294">
+        <f t="shared" si="14"/>
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="295" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A295">
         <v>295</v>
       </c>
       <c r="B295" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="C295" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D295" t="s">
         <v>21</v>
@@ -8532,18 +12108,30 @@
         <v>311</v>
       </c>
       <c r="F295" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.6">
+        <v>624</v>
+      </c>
+      <c r="H295" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I295" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L295">
+        <f t="shared" si="14"/>
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="296" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A296">
         <v>296</v>
       </c>
       <c r="B296" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C296" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D296" t="s">
         <v>26</v>
@@ -8552,27 +12140,51 @@
         <v>222</v>
       </c>
       <c r="F296" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.6">
+        <v>552</v>
+      </c>
+      <c r="H296" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I296" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L296">
+        <f t="shared" si="14"/>
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="297" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A297">
         <v>297</v>
       </c>
       <c r="B297" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C297" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D297" t="s">
         <v>26</v>
       </c>
       <c r="E297" t="s">
-        <v>311</v>
+        <v>276</v>
       </c>
       <c r="F297" t="s">
-        <v>627</v>
+        <v>625</v>
+      </c>
+      <c r="H297" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I297" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L297">
+        <f t="shared" si="14"/>
+        <v>1297</v>
       </c>
     </row>
   </sheetData>

--- a/tier.xlsx
+++ b/tier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyung\Desktop\새 폴더 (1)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE520E0C-F7FE-4A48-9F4F-6AD5E15BFD95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{353D880D-7B2F-41EF-8E60-F4D904BE294B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{B5D2F30C-64E4-4785-A390-F7C9B2DB27D6}"/>
   </bookViews>
@@ -7211,7 +7211,10 @@
       </c>
       <c r="I142" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1141.mp4</v>
+      </c>
+      <c r="K142">
+        <v>1</v>
       </c>
       <c r="L142">
         <f t="shared" si="8"/>
@@ -7531,9 +7534,12 @@
       </c>
       <c r="I152" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1151.mp4</v>
       </c>
       <c r="J152">
+        <v>1</v>
+      </c>
+      <c r="K152">
         <v>1</v>
       </c>
       <c r="L152">
@@ -7822,7 +7828,10 @@
       </c>
       <c r="I161" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1160.mp4</v>
+      </c>
+      <c r="K161">
+        <v>1</v>
       </c>
       <c r="L161">
         <f t="shared" si="8"/>
@@ -7950,7 +7959,10 @@
       </c>
       <c r="I165" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1164.mp4</v>
+      </c>
+      <c r="K165">
+        <v>1</v>
       </c>
       <c r="L165">
         <f t="shared" si="8"/>
@@ -8270,7 +8282,10 @@
       </c>
       <c r="I175" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1174.mp4</v>
+      </c>
+      <c r="K175">
+        <v>1</v>
       </c>
       <c r="L175">
         <f t="shared" si="8"/>
@@ -8558,7 +8573,10 @@
       </c>
       <c r="I184" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>1183.mp4</v>
+      </c>
+      <c r="K184">
+        <v>1</v>
       </c>
       <c r="L184">
         <f t="shared" si="8"/>
@@ -8942,7 +8960,10 @@
       </c>
       <c r="I196" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1195.mp4</v>
+      </c>
+      <c r="K196">
+        <v>1</v>
       </c>
       <c r="L196">
         <f t="shared" si="11"/>
@@ -9166,9 +9187,12 @@
       </c>
       <c r="I203" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1202.mp4</v>
       </c>
       <c r="J203">
+        <v>1</v>
+      </c>
+      <c r="K203">
         <v>1</v>
       </c>
       <c r="L203">
@@ -9265,7 +9289,10 @@
       </c>
       <c r="I206" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1205.mp4</v>
+      </c>
+      <c r="K206">
+        <v>1</v>
       </c>
       <c r="L206">
         <f t="shared" si="11"/>
@@ -10289,7 +10316,10 @@
       </c>
       <c r="I238" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1238.mp4</v>
+      </c>
+      <c r="K238">
+        <v>1</v>
       </c>
       <c r="L238">
         <f t="shared" si="11"/>
@@ -10449,7 +10479,10 @@
       </c>
       <c r="I243" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1243.mp4</v>
+      </c>
+      <c r="K243">
+        <v>1</v>
       </c>
       <c r="L243">
         <f t="shared" si="11"/>
@@ -11348,7 +11381,10 @@
       </c>
       <c r="I271" t="str">
         <f t="shared" si="13"/>
-        <v/>
+        <v>1271.mp4</v>
+      </c>
+      <c r="K271">
+        <v>1</v>
       </c>
       <c r="L271">
         <f t="shared" si="14"/>
@@ -11732,7 +11768,10 @@
       </c>
       <c r="I283" t="str">
         <f t="shared" si="13"/>
-        <v/>
+        <v>1283.mp4</v>
+      </c>
+      <c r="K283">
+        <v>1</v>
       </c>
       <c r="L283">
         <f t="shared" si="14"/>

--- a/tier.xlsx
+++ b/tier.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyung\Desktop\새 폴더 (3)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2025 스타\2 mstzsite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3583DF3F-68CC-497E-894F-1291128299E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA516468-44A5-43FD-A7B4-CDAAB53226B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{B5D2F30C-64E4-4785-A390-F7C9B2DB27D6}"/>
   </bookViews>
@@ -4132,7 +4132,7 @@
         <v>40</v>
       </c>
       <c r="C31" t="s">
-        <v>10</v>
+        <v>313</v>
       </c>
       <c r="D31" t="s">
         <v>21</v>

--- a/tier.xlsx
+++ b/tier.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2025 스타\2 mstzsite\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2025 스타\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA516468-44A5-43FD-A7B4-CDAAB53226B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43DAEA85-77E3-425A-B185-96075965A526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{B5D2F30C-64E4-4785-A390-F7C9B2DB27D6}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="688">
   <si>
     <t>순번</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2656,6 +2656,62 @@
   <si>
     <t>경콩</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>깅예솔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>씨나인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yunhee1222</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유성민</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0티어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>goodgame07</t>
+  </si>
+  <si>
+    <t>휘연</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타마양</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진서랄까</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JSA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rldyal71</t>
+  </si>
+  <si>
+    <t>tamama88</t>
+  </si>
+  <si>
+    <t>janjanoo</t>
   </si>
 </sst>
 </file>
@@ -3037,7 +3093,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54A2A291-B3BF-4EBE-93A6-386812DCA76D}">
-  <dimension ref="A1:Q302"/>
+  <dimension ref="A1:Q307"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="2" max="2" width="10.9375" bestFit="1" customWidth="1"/>
@@ -4132,7 +4188,7 @@
         <v>40</v>
       </c>
       <c r="C31" t="s">
-        <v>313</v>
+        <v>10</v>
       </c>
       <c r="D31" t="s">
         <v>21</v>
@@ -6254,7 +6310,7 @@
         <v>106</v>
       </c>
       <c r="C96" t="s">
-        <v>323</v>
+        <v>10</v>
       </c>
       <c r="D96" t="s">
         <v>26</v>
@@ -8367,7 +8423,7 @@
         <v>173</v>
       </c>
       <c r="C161" t="s">
-        <v>10</v>
+        <v>310</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -11701,7 +11757,7 @@
         <v/>
       </c>
       <c r="L261">
-        <f t="shared" ref="L261:L302" si="20">1000+A261</f>
+        <f t="shared" ref="L261:L307" si="20">1000+A261</f>
         <v>1259</v>
       </c>
     </row>
@@ -12999,6 +13055,9 @@
       <c r="B302" t="s">
         <v>642</v>
       </c>
+      <c r="C302" t="s">
+        <v>325</v>
+      </c>
       <c r="D302" t="s">
         <v>643</v>
       </c>
@@ -13011,6 +13070,126 @@
       <c r="L302">
         <f t="shared" si="20"/>
         <v>1300</v>
+      </c>
+    </row>
+    <row r="303" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A303">
+        <v>301</v>
+      </c>
+      <c r="B303" t="s">
+        <v>673</v>
+      </c>
+      <c r="C303" t="s">
+        <v>674</v>
+      </c>
+      <c r="D303" t="s">
+        <v>675</v>
+      </c>
+      <c r="E303" t="s">
+        <v>222</v>
+      </c>
+      <c r="F303" t="s">
+        <v>676</v>
+      </c>
+      <c r="L303">
+        <f t="shared" si="20"/>
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="304" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A304">
+        <v>302</v>
+      </c>
+      <c r="B304" t="s">
+        <v>677</v>
+      </c>
+      <c r="C304" t="s">
+        <v>325</v>
+      </c>
+      <c r="D304" t="s">
+        <v>678</v>
+      </c>
+      <c r="E304" t="s">
+        <v>679</v>
+      </c>
+      <c r="F304" t="s">
+        <v>680</v>
+      </c>
+      <c r="L304">
+        <f t="shared" si="20"/>
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="305" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A305">
+        <v>303</v>
+      </c>
+      <c r="B305" t="s">
+        <v>681</v>
+      </c>
+      <c r="C305" t="s">
+        <v>684</v>
+      </c>
+      <c r="D305" t="s">
+        <v>678</v>
+      </c>
+      <c r="E305" t="s">
+        <v>309</v>
+      </c>
+      <c r="F305" t="s">
+        <v>685</v>
+      </c>
+      <c r="L305">
+        <f t="shared" si="20"/>
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="306" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A306">
+        <v>304</v>
+      </c>
+      <c r="B306" t="s">
+        <v>682</v>
+      </c>
+      <c r="C306" t="s">
+        <v>684</v>
+      </c>
+      <c r="D306" t="s">
+        <v>675</v>
+      </c>
+      <c r="E306" t="s">
+        <v>309</v>
+      </c>
+      <c r="F306" t="s">
+        <v>686</v>
+      </c>
+      <c r="L306">
+        <f t="shared" si="20"/>
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="307" spans="1:12" x14ac:dyDescent="0.6">
+      <c r="A307">
+        <v>305</v>
+      </c>
+      <c r="B307" t="s">
+        <v>683</v>
+      </c>
+      <c r="C307" t="s">
+        <v>325</v>
+      </c>
+      <c r="D307" t="s">
+        <v>675</v>
+      </c>
+      <c r="E307" t="s">
+        <v>309</v>
+      </c>
+      <c r="F307" t="s">
+        <v>687</v>
+      </c>
+      <c r="L307">
+        <f t="shared" si="20"/>
+        <v>1305</v>
       </c>
     </row>
   </sheetData>

--- a/tier.xlsx
+++ b/tier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2025 스타\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43DAEA85-77E3-425A-B185-96075965A526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7743F66-969E-41D4-A2AA-1C520F9A24DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{B5D2F30C-64E4-4785-A390-F7C9B2DB27D6}"/>
   </bookViews>
@@ -4517,7 +4517,7 @@
         <v>49</v>
       </c>
       <c r="C41" t="s">
-        <v>10</v>
+        <v>317</v>
       </c>
       <c r="D41" t="s">
         <v>26</v>

--- a/tier.xlsx
+++ b/tier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2025 스타\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7743F66-969E-41D4-A2AA-1C520F9A24DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A75FEBF3-E57D-4037-BA35-B147AB3B7F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14595" yWindow="32280" windowWidth="29040" windowHeight="17520" xr2:uid="{B5D2F30C-64E4-4785-A390-F7C9B2DB27D6}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="688">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="689">
   <si>
     <t>순번</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2712,6 +2712,10 @@
   </si>
   <si>
     <t>janjanoo</t>
+  </si>
+  <si>
+    <t>신세계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3170,7 +3174,7 @@
         <v>328</v>
       </c>
       <c r="G2" s="1">
-        <v>46167</v>
+        <v>46182</v>
       </c>
       <c r="H2" t="str">
         <f>IF(J2=1,L2&amp;".png","")</f>
@@ -3891,7 +3895,7 @@
         <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>10</v>
+        <v>688</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -4025,7 +4029,7 @@
         <v>35</v>
       </c>
       <c r="C26" t="s">
-        <v>323</v>
+        <v>10</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -6342,7 +6346,7 @@
         <v>107</v>
       </c>
       <c r="C97" t="s">
-        <v>323</v>
+        <v>10</v>
       </c>
       <c r="D97" t="s">
         <v>26</v>
@@ -6630,7 +6634,7 @@
         <v>116</v>
       </c>
       <c r="C106" t="s">
-        <v>10</v>
+        <v>323</v>
       </c>
       <c r="D106" t="s">
         <v>21</v>
@@ -7529,7 +7533,7 @@
         <v>146</v>
       </c>
       <c r="C134" t="s">
-        <v>10</v>
+        <v>688</v>
       </c>
       <c r="D134" t="s">
         <v>21</v>
@@ -8554,7 +8558,7 @@
         <v>177</v>
       </c>
       <c r="C165" t="s">
-        <v>323</v>
+        <v>10</v>
       </c>
       <c r="D165" t="s">
         <v>21</v>
@@ -10045,7 +10049,7 @@
         <v>225</v>
       </c>
       <c r="C210" t="s">
-        <v>10</v>
+        <v>688</v>
       </c>
       <c r="D210" t="s">
         <v>21</v>
@@ -10412,7 +10416,7 @@
         <v>236</v>
       </c>
       <c r="C221" t="s">
-        <v>10</v>
+        <v>321</v>
       </c>
       <c r="D221" t="s">
         <v>26</v>
@@ -12057,7 +12061,7 @@
         <v>287</v>
       </c>
       <c r="C271" t="s">
-        <v>10</v>
+        <v>688</v>
       </c>
       <c r="D271" t="s">
         <v>26</v>
@@ -13104,7 +13108,7 @@
         <v>677</v>
       </c>
       <c r="C304" t="s">
-        <v>325</v>
+        <v>10</v>
       </c>
       <c r="D304" t="s">
         <v>678</v>
